--- a/2026-11-01/weekly-2026-11-01.xlsx
+++ b/2026-11-01/weekly-2026-11-01.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,9 +31,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;#&quot;0"/>
-    <numFmt numFmtId="165" formatCode="+#,##0"/>
+    <numFmt numFmtId="165" formatCode="+#,##0&quot; 🚀&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot; ★&quot;"/>
-    <numFmt numFmtId="167" formatCode="+#,##0&quot; 🚀&quot;"/>
+    <numFmt numFmtId="167" formatCode="+#,##0"/>
     <numFmt numFmtId="168" formatCode="&quot;PH #&quot;0"/>
     <numFmt numFmtId="169" formatCode="#,##0&quot; 票&quot;"/>
   </numFmts>
@@ -88,6 +88,12 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00C2410C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <color rgb="001D4ED8"/>
       <sz val="10"/>
       <u val="single"/>
@@ -109,12 +115,6 @@
       <color rgb="00A0A0A0"/>
       <sz val="10"/>
       <u val="single"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00C2410C"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -141,17 +141,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF6EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE4CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -230,6 +230,60 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -242,8 +296,8 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,133 +311,82 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -396,10 +399,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -890,10 +893,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="78" customHeight="1">
+    <row r="4" ht="106" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>TradingAgents</t>
+          <t>🚀 TradingAgents</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -907,10 +910,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>381</v>
+        <v>1776</v>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
@@ -919,7 +922,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>10-26 #6 +381</t>
+          <t>10-26 #6 +381 → 10-27 #2 +1,395🚀</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -934,7 +937,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>清华大学计算机学士（2018–2022，导师唐杰）；UCLA 计算机博士在读（2022–，导师 Wei Wang）</t>
+          <t>清华大学计算机学士（2018–2022，导师唐杰）；UCLA 计算机博士在读（2022–，导师 Wei Wang；主页写 fourth-year Ph.D. candidate）</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -962,7 +965,7 @@
               <color rgb="001F2937"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve"> Cloud AI Research、AWS；Amazon PhD Fellowship 2026</t>
+            <t xml:space="preserve"> Cloud AI Research、AWS、NEC Labs；Amazon PhD Fellowship 2026（今日复核主页仍准确）</t>
           </r>
         </is>
       </c>
@@ -995,22 +998,152 @@
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>来源1、来源2、来源3、来源4、来源5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="148" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
+          <t>huashu-design</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Agent 设计 skill（Huashu Design 3.0）</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：一句话生成可交付网页/App 原型/可编辑 PPTX/动画/信息图，含风格库与设计体检</t>
+          </r>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>251</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>10-27 #13 +251</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>作者 / 独立开发者；huashu-design、nuwa-skill 等开源 skill 作者</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>华中科技大学经济学专业（理科）本科</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>互联网约 10 年，主要做用户研究与产品运营；曾就职</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>美团</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>，2023 年 3 月离职后做 AI 自媒体与独立开发；产品含「小猫补光灯」；著《一本书玩转DeepSeek》；为微软/美团/北大等做过 AI 分享与培训</t>
+          </r>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>China（GitHub location）；小红书 IP 属地显示云南；固定定居城市未查到（自述近年多国旅居）</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>alchaincyf@gmail.com</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>X
+alchain
+花叔
+Alchian花生
+个人站
+GitHub
+AI进化论-花生 / 花叔
+花叔（只工作不上班版）</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4、来源5、来源6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1031,269 +1164,370 @@
           </r>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>深圳市揽岳智能科技有限公司法定代表人、董事长兼经理</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
         <is>
           <t>未查到（公开报道多写柔宇联合创始人为清华/斯坦福校友群体，未单独证实其学历）</t>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t>柔宇科技联合创始人之一、曾任副总裁（与刘自鸿、魏鹏等）；2025 转向 AI 云端浏览器基础设施创业，创立揽岳智能 / Lexmount</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>深圳（公司注册地）；北京亦有运营主体</t>
         </is>
       </c>
-      <c r="M5" s="20" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N5" s="20" t="inlineStr">
+      <c r="N6" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O5" s="21" t="inlineStr">
+      <c r="O6" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P5" s="20" t="inlineStr">
+      <c r="P6" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="Q5" s="15" t="inlineStr">
+      <c r="Q6" s="24" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="19" t="inlineStr">
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="31" t="n"/>
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>Moli 核心开发者 / PH maker；lexmount/moli 主要贡献者</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="J7" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t>北京开发者；在创业公司做浏览器相关，主导开源 Moli；V2EX 发帖介绍项目</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>北京（GitHub Location: Beijing China）</t>
         </is>
       </c>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr">
+      <c r="N7" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="O7" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P6" s="15" t="inlineStr">
+      <c r="P7" s="24" t="inlineStr">
         <is>
           <t>GitHub
 v2ex</t>
         </is>
       </c>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="Q7" s="24" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="23" t="n"/>
-      <c r="B7" s="23" t="n"/>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="n"/>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="23" t="n"/>
-      <c r="H7" s="19" t="inlineStr">
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="32" t="n"/>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>Nico Hu</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>PH maker（自称 one of the makers of Moli by Lexmount）</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J8" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K7" s="20" t="inlineStr">
+      <c r="K8" s="29" t="inlineStr">
         <is>
           <t>未查到可靠公开履历（同名 LinkedIn 多为生物医药，未核实为同一人）</t>
         </is>
       </c>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="L8" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="M7" s="20" t="inlineStr">
+      <c r="M8" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr">
+      <c r="N8" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O7" s="21" t="inlineStr">
+      <c r="O8" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr">
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="Q7" s="24" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+    <row r="9" ht="106" customHeight="1">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>智能体工具</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="00A0A0A0"/>
+              <sz val="10"/>
+            </rPr>
+            <t>给 AI Agent 的互联网读写 CLI</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="00A0A0A0"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：Twitter/Reddit/YouTube/GitHub/Bilibili/小红书等，一条命令、尽量零 API 费用</t>
+          </r>
+        </is>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="38" t="n">
+        <v>746</v>
+      </c>
+      <c r="F9" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>10-13/27 #10 +746</t>
+        </is>
+      </c>
+      <c r="H9" s="40" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>Solo founder / 主要作者与维护者（华人主导：中文 README、foxmail、Bilibili/小红书渠道、UTC+8 活跃）</t>
+        </is>
+      </c>
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K9" s="36" t="inlineStr">
+        <is>
+          <t>自称 Solo founder（All employees are AI）；主导 Agent-Reach、xfetch 等开源项目；自 2020 年起在 GitHub 活跃</t>
+        </is>
+      </c>
+      <c r="L9" s="29" t="inlineStr">
+        <is>
+          <t>未查到（个人页标注 When I Code UTC+8，不足以定城市）</t>
+        </is>
+      </c>
+      <c r="M9" s="36" t="inlineStr">
+        <is>
+          <t>pnt01@foxmail.com</t>
+        </is>
+      </c>
+      <c r="N9" s="29" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O9" s="30" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P9" s="36" t="inlineStr">
+        <is>
+          <t>X
+GitHub
+discord</t>
+        </is>
+      </c>
+      <c r="Q9" s="36" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4、来源5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>ziwei-doushu</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>紫微斗数开源排盘引擎（倪海厦《天纪》体系）+ 67.5 万命盘×13 维解读数据集 v4.0；商业站 metisziwei.com</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D10" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E10" s="42" t="n">
         <v>199</v>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F10" s="43" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>10-25/26 #7 +199</t>
         </is>
       </c>
-      <c r="H8" s="31" t="inlineStr">
+      <c r="H10" s="40" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I10" s="36" t="inlineStr">
         <is>
           <t>作者 / Metis 创始人，自称一人用 AI 做出商业化 SaaS</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J10" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K10" s="36" t="inlineStr">
         <is>
           <t>Metis紫微创始人；称专业版订阅超 800、注册超 1 万</t>
         </is>
       </c>
-      <c r="L8" s="27" t="inlineStr">
+      <c r="L10" s="36" t="inlineStr">
         <is>
           <t>重庆（运营主体注册地）</t>
         </is>
       </c>
-      <c r="M8" s="27" t="inlineStr">
+      <c r="M10" s="36" t="inlineStr">
         <is>
           <t>wdy778@outlook.com</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N10" s="29" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="O10" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P8" s="27" t="inlineStr">
+      <c r="P10" s="36" t="inlineStr">
         <is>
           <t>X
 王多鱼AI2.0
@@ -1301,31 +1535,33 @@
 GitHub</t>
         </is>
       </c>
-      <c r="Q8" s="27" t="inlineStr">
+      <c r="Q10" s="36" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q8"/>
+  <autoFilter ref="A3:Q10"/>
   <mergeCells count="9">
-    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F6:F8"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1339,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1433,121 +1669,121 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>🚀 hallmark</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
-        <is>
-          <t>总星 33,716，「反 AI 味」设计 skill，星增约昨日 2.9×</t>
-        </is>
-      </c>
-      <c r="E4" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="36" t="n">
-        <v>1317</v>
-      </c>
-      <c r="G4" s="37" t="n">
-        <v>1317</v>
-      </c>
-      <c r="H4" s="38" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>总星 36,265，「反 AI 味」设计 skill，给 Claude Code / Cursor / Codex</t>
+        </is>
+      </c>
+      <c r="E4" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="45" t="n">
+        <v>3561</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>2244</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="34" t="inlineStr">
-        <is>
-          <t>10-26 #2 +1,317🚀</t>
-        </is>
-      </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>10-26 #2 +1,317🚀 → 10-27 #1 +2,244🚀</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Hassan El Mghari</t>
         </is>
       </c>
-      <c r="K4" s="34" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Nutlope；非华人</t>
         </is>
       </c>
-      <c r="L4" s="40" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>🚀 impeccable</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
-        <is>
-          <t>总星 87,669，让 AI 编程工具更懂设计的设计语言</t>
-        </is>
-      </c>
-      <c r="E5" s="41" t="n">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>总星 89,168，让 AI 编程工具更懂设计的设计语言</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="36" t="n">
-        <v>1092</v>
-      </c>
-      <c r="G5" s="37" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H5" s="38" t="inlineStr">
+      <c r="F5" s="45" t="n">
+        <v>2598</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>1506</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="34" t="inlineStr">
-        <is>
-          <t>10-26 #4 +1,092🚀</t>
-        </is>
-      </c>
-      <c r="J5" s="39" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>Paul Bakaus</t>
         </is>
       </c>
-      <c r="K5" s="34" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="40" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="50" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>cindy</t>
+          <t>🚀 cindy</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1562,17 +1798,17 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>总星 4,838，心动出品的开源开箱即用 AI Agent</t>
-        </is>
-      </c>
-      <c r="E6" s="42" t="n">
+          <t>总星 6,439，心动出品的开源开箱即用 AI Agent</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>675</v>
-      </c>
-      <c r="G6" s="43" t="n">
-        <v>675</v>
+      <c r="F6" s="45" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1296</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -1581,7 +1817,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>10-26 #1 +675</t>
+          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -1591,7 +1827,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>XD；官方项目，CEO 黄一孟主导，按规则不算独立项目</t>
+          <t>XD；官方项目，不计独立</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
@@ -1601,224 +1837,240 @@
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>🚀 microduck</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>总星 11,616，迷你双足小鸭机器人 🦆</t>
-        </is>
-      </c>
-      <c r="E7" s="41" t="n">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>总星 12,395，迷你双足小鸭机器人 🦆</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="36" t="n">
-        <v>647</v>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>647</v>
-      </c>
-      <c r="H7" s="38" t="inlineStr">
+      <c r="F7" s="45" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>843</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="34" t="inlineStr">
-        <is>
-          <t>10-26 #5 +647🚀</t>
-        </is>
-      </c>
-      <c r="J7" s="39" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>10-26 #5 +647🚀 → 10-27 #8 +843</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Pollen Robotics</t>
         </is>
       </c>
-      <c r="K7" s="34" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="33" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>法国</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="50" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>🚀 thinkrail</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>开发工具</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>总星 2,874，JetBrains 轻量 Vibe Coding IDE（围绕 pi 定制）</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>1224</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>1173</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>JetBrains 官方</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>ECC</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>安全</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>总星 289,824，Agent harness 性能优化系统</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：skills / instincts / memory / 安全与研究优先开发</t>
+          </r>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>896</v>
+      </c>
+      <c r="G9" s="47" t="n">
+        <v>896</v>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>10-27 #5 +896</t>
+        </is>
+      </c>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>Affaan Mustafa</t>
+        </is>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>Jump Trading；非华人</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
           <t>claude-seo</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>今日 +197 ⭐，总星 20,832，Claude Code 通用 SEO skill（26 子技能 + 19 子智能体）</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E10" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F10" s="48" t="n">
         <v>197</v>
       </c>
-      <c r="G8" s="43" t="n">
+      <c r="G10" s="49" t="n">
         <v>197</v>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>10-26 #11 +197</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J10" s="28" t="inlineStr">
         <is>
           <t>Agrici Daniel，未核实为华人</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="K10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>coolify</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>今日 +152 ⭐，总星 64,352，可自托管的开源 PaaS（类 Vercel / Heroku）</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" s="44" t="n">
-        <v>152</v>
-      </c>
-      <c r="G9" s="45" t="n">
-        <v>152</v>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>10-26 #9 +152</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
-        <is>
-          <t>coolLabs</t>
-        </is>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>非华人主导</t>
-        </is>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>欧洲开源</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>thinkrail</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>开发工具</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>总星 1,700，JetBrains 轻量 Vibe Coding IDE</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="G10" s="43" t="n">
-        <v>51</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>10-26 #8 +51</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>JetBrains 官方</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -1827,293 +2079,405 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
+          <t>postiz-app</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>总星 38,431，开源 agentic 社媒排程工具</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>188</v>
+      </c>
+      <c r="G11" s="47" t="n">
+        <v>188</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>10-27 #12 +188</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>Gitroom</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>Israel；非华人主导</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>openbot</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>今日 +176 ⭐，总星 1,457，本地优先桌面工作区，持久 AI 队友（Codex / Claude / Grok）</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>176</v>
+      </c>
+      <c r="G12" s="49" t="n">
+        <v>176</v>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>10-27 #9 +176</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>未发现华人主导</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Strawberry 1.0</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>内置 AI Companions 的浏览器，替团队干调研 / 跟进 / 行政杂活</t>
+        </is>
+      </c>
+      <c r="E13" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="52" t="n">
+        <v>265</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>10-26 #1</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>未发现华人主导</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
           <t>Moli by Lexmount</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>给 Agent 用的最快无头浏览器引擎</t>
         </is>
       </c>
-      <c r="E11" s="46" t="n">
+      <c r="E14" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H14" s="53" t="n">
         <v>234</v>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>10-25 #1</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>昨日华人项，今日跌出 PH 日榜</t>
+        </is>
+      </c>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>SurgePix</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>可分层编辑的 AI 视觉工具，也开放 agent skills</t>
+        </is>
+      </c>
+      <c r="E15" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="52" t="n">
+        <v>212</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>10-26 #2</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>未发现华人主导</t>
+        </is>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>AgentGrid.io</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>MiniMax M3.1 Flash</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>人与智能体共用的协作工作区</t>
-        </is>
-      </c>
-      <c r="E12" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="49" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>MiniMax 新 Flash 模型，号称 agent 场景约快 3×、便宜 70%</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="49" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="50" t="n">
-        <v>169</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>10-25 #2</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>YC；公开讨论者含 Avishay Cohen / Omri Ben-Shoham 等，未发现华人主导</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="H16" s="53" t="n">
+        <v>171</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>10-26 #3</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>MiniMax 大厂官方模型发布，不计独立华人项目</t>
+        </is>
+      </c>
+      <c r="K16" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L16" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Badgey</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>把 iPhone 变成朝外的姓名牌</t>
-        </is>
-      </c>
-      <c r="E13" s="51" t="n">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>VoiceStudio</t>
+        </is>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>总星 89,187，本地开源 ElevenLabs 替代，语音克隆 / 配音 / 多语种</t>
+        </is>
+      </c>
+      <c r="E17" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F17" s="38" t="n">
+        <v>3889</v>
+      </c>
+      <c r="G17" s="57" t="n">
+        <v>2297</v>
+      </c>
+      <c r="H17" s="39" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="I17" s="36" t="inlineStr">
+        <is>
+          <t>10-18/26 #3 +1,592 → 10-27 #11 +2,297</t>
+        </is>
+      </c>
+      <c r="J17" s="40" t="inlineStr">
+        <is>
+          <t>Deb Palash，未核实为华人</t>
+        </is>
+      </c>
+      <c r="K17" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="47" t="n">
-        <v>167</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>10-25 #3</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>未发现华人主导</t>
-        </is>
-      </c>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="L17" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Openstatus Incident Management</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>小团队的开源事故管理</t>
-        </is>
-      </c>
-      <c r="E14" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="50" t="n">
-        <v>142</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>10-25 #4</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>openstatus</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>Thibault Le Ouay 等；欧洲</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>VoiceStudio</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>592 ⭐，总星 86,770，本地开源 ElevenLabs 替代，语音克隆 / 配音 / 646 语种</t>
-        </is>
-      </c>
-      <c r="E15" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="54" t="n">
-        <v>1592</v>
-      </c>
-      <c r="G15" s="55" t="n">
-        <v>1592</v>
-      </c>
-      <c r="H15" s="56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="27" t="inlineStr">
-        <is>
-          <t>10-18/26 #3 +1,592</t>
-        </is>
-      </c>
-      <c r="J15" s="31" t="inlineStr">
-        <is>
-          <t>Deb Palash，未核实为华人</t>
-        </is>
-      </c>
-      <c r="K15" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:L15"/>
+  <autoFilter ref="A3:L17"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
@@ -2131,6 +2495,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2152,92 +2518,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="57" t="inlineStr">
+      <c r="B1" s="58" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-26 – 11-01）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="58" t="inlineStr">
-        <is>
-          <t>全球项目 12 个 · 华人项目 3 个 · 核心人物 5 位</t>
+      <c r="B2" s="59" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 5 个 · 核心人物 7 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-26（第 1/7 天），每天日报后自动刷新。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-27（第 2/7 天），每天日报后自动刷新。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 debpalash/VoiceStudio；已收录全球项目 12 个、华人项目 3 个。</t>
+      <c r="B6" s="62" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 debpalash/VoiceStudio；已收录全球项目 14 个、华人项目 5 个，今日新增华人项目：alchaincyf/huashu-design、Panniantong/Agent-Reach。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="62" t="inlineStr">
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="63" t="inlineStr">
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="64" t="inlineStr">
+      <c r="B11" s="65" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="65" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="66" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-11-01/</t>
         </is>
@@ -2258,7 +2624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2310,27 +2676,27 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E4" s="67" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>https://github.com/Yijia-Xiao</t>
         </is>
@@ -2357,36 +2723,36 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>https://yijia-xiao.com/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E6" s="67" t="inlineStr">
-        <is>
-          <t>https://yijia-xiao.com/assets/YIJIA_XIAO-CV.pdf</t>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>https://github.com/TauricResearch/TradingAgents</t>
         </is>
       </c>
     </row>
@@ -2411,252 +2777,252 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
-        <is>
-          <t>https://github.com/TauricResearch/TradingAgents</t>
+      <c r="E7" s="68" t="inlineStr">
+        <is>
+          <t>https://tauric.ai/contact/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E8" s="67" t="inlineStr">
-        <is>
-          <t>https://tauric.ai/contact/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>https://tauric.ai/research/tradingagents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>TauricResearch/TradingAgents</t>
+          <t>alchaincyf/huashu-design</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>肖一嘉（Yijia Xiao）</t>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="68" t="inlineStr">
+        <is>
+          <t>https://x.com/AlchainHust</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>https://www.huasheng.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E11" s="68" t="inlineStr">
+        <is>
+          <t>https://github.com/alchaincyf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>https://www.huasheng.ai/insights/wechat-2247485096-1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E13" s="68" t="inlineStr">
+        <is>
+          <t>https://www.huasheng.ai/consulting/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>来源5</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>https://tauric.ai/research/tradingagents</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>https://github.com/alchaincyf/huashu-design</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>来源6</t>
+        </is>
+      </c>
+      <c r="E15" s="68" t="inlineStr">
+        <is>
+          <t>https://m.okjike.com/users/27BF807A-FA4D-4B01-AAFD-05FAAA674335</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E10" s="67" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>https://wenjiai.cn/products/lanyue-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>https://vc.pedaily.cn/company/865282.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E12" s="67" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/about</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/privacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>来源5</t>
-        </is>
-      </c>
-      <c r="E14" s="67" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>https://github.com/ldm0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>v2ex</t>
-        </is>
-      </c>
-      <c r="E16" s="67" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1236833</t>
         </is>
       </c>
     </row>
@@ -2668,7 +3034,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Donough Liu（GitHub ldm0）</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -2681,36 +3047,36 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>https://github.com/lexmount/moli</t>
+      <c r="E17" s="68" t="inlineStr">
+        <is>
+          <t>https://vc.pedaily.cn/company/865282.html</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E18" s="67" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/about</t>
         </is>
       </c>
     </row>
@@ -2722,61 +3088,61 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Nico Hu</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E19" s="68" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/privacy</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Nico Hu</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E20" s="67" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>来源5</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>Renhuai123/ziwei-doushu</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
+          <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -2786,51 +3152,51 @@
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>https://x.com/wdy188</t>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E21" s="68" t="inlineStr">
+        <is>
+          <t>https://github.com/ldm0</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E22" s="67" t="inlineStr">
-        <is>
-          <t>https://github.com/Renhuai123</t>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>v2ex</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1236833</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>Renhuai123/ziwei-doushu</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
+          <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -2843,68 +3209,392 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>https://github.com/Renhuai123/ziwei-doushu</t>
+      <c r="E23" s="68" t="inlineStr">
+        <is>
+          <t>https://github.com/lexmount/moli</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E24" s="67" t="inlineStr">
-        <is>
-          <t>https://metisziwei.com/privacy</t>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Nico Hu</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E25" s="68" t="inlineStr">
+        <is>
+          <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Nico Hu</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E27" s="68" t="inlineStr">
+        <is>
+          <t>https://x.com/Neo_Reidlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>discord</t>
+        </is>
+      </c>
+      <c r="E29" s="68" t="inlineStr">
+        <is>
+          <t>https://discord.gg/NSZz22R39</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E30" s="33" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E31" s="68" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E32" s="33" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E33" s="68" t="inlineStr">
+        <is>
+          <t>https://x.com/wdy188</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>https://github.com/Renhuai123</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E35" s="68" t="inlineStr">
+        <is>
+          <t>https://github.com/Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E36" s="33" t="inlineStr">
+        <is>
+          <t>https://metisziwei.com/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E37" s="68" t="inlineStr">
         <is>
           <t>https://zamantika.com/profile/wdy188</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E25"/>
+  <autoFilter ref="A3:E37"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -2932,6 +3622,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId34"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-11-01/weekly-2026-11-01.xlsx
+++ b/2026-11-01/weekly-2026-11-01.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -284,6 +284,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -296,91 +297,84 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -402,7 +396,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -770,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,18 +996,210 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="148" customHeight="1">
+    <row r="5" ht="92" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
+          <t>DeepTutor</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>港大 HKUDS 开源的 agent 原生个性化 AI 家教</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：引用溯源解题辅导 + 按难度出题 + 学习者记忆闭环</t>
+          </r>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>1598</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>10-28 #9 +1,598</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>主要作者（GitHub pancacake，贡献居首）、论文共同一作</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>北京交通大学电子与通信工程本科（2023–2027 预计）；北大附中（2017–2023）；港大计算与数据科学学院 Year-0 博士（导师黄超）</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>港大</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Data Intelligence Lab 研究助理；中科院自动化所 3DV Lab、清华 AIR、Lancaster 大学（远程）、北交大软件学院实习；另发布 CatchMe</t>
+          </r>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>北京 / 香港（就读地，常住城市未查到）</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>个人站
+GitHub</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="22" t="n"/>
+      <c r="B6" s="22" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="22" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>HKUDS 负责人、论文通讯作者</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>University of Notre Dame 计算机博士</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>港大</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>计算机系与数据科学学院助理教授；带队 LightRAG、CLI-Anything 等</t>
+          </r>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>chuang@cs.hku.hk</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>个人站
+GitHub 组织</t>
+        </is>
+      </c>
+      <c r="Q6" s="15" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="148" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
           <t>huashu-design</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1034,38 +1220,38 @@
           </r>
         </is>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D7" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E7" s="27" t="n">
         <v>251</v>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10-27 #13 +251</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t>作者 / 独立开发者；huashu-design、nuwa-skill 等开源 skill 作者</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t>华中科技大学经济学专业（理科）本科</t>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1094,27 +1280,27 @@
           </r>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="L7" s="25" t="inlineStr">
         <is>
           <t>China（GitHub location）；小红书 IP 属地显示云南；固定定居城市未查到（自述近年多国旅居）</t>
         </is>
       </c>
-      <c r="M5" s="15" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t>alchaincyf@gmail.com</t>
         </is>
       </c>
-      <c r="N5" s="20" t="inlineStr">
+      <c r="N7" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O5" s="21" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P5" s="15" t="inlineStr">
+      <c r="P7" s="25" t="inlineStr">
         <is>
           <t>X
 alchain
@@ -1126,24 +1312,24 @@
 花叔（只工作不上班版）</t>
         </is>
       </c>
-      <c r="Q5" s="15" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5、来源6</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1164,208 +1350,208 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="H8" s="19" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>深圳市揽岳智能科技有限公司法定代表人、董事长兼经理</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>未查到（公开报道多写柔宇联合创始人为清华/斯坦福校友群体，未单独证实其学历）</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>柔宇科技联合创始人之一、曾任副总裁（与刘自鸿、魏鹏等）；2025 转向 AI 云端浏览器基础设施创业，创立揽岳智能 / Lexmount</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
+      <c r="L8" s="15" t="inlineStr">
         <is>
           <t>深圳（公司注册地）；北京亦有运营主体</t>
         </is>
       </c>
-      <c r="M6" s="29" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N6" s="29" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O6" s="30" t="inlineStr">
+      <c r="O8" s="21" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P6" s="29" t="inlineStr">
+      <c r="P8" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="Q6" s="24" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="31" t="n"/>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="28" t="inlineStr">
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="33" t="n"/>
+      <c r="B9" s="33" t="n"/>
+      <c r="C9" s="33" t="n"/>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="33" t="n"/>
+      <c r="F9" s="33" t="n"/>
+      <c r="G9" s="33" t="n"/>
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>Moli 核心开发者 / PH maker；lexmount/moli 主要贡献者</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>北京开发者；在创业公司做浏览器相关，主导开源 Moli；V2EX 发帖介绍项目</t>
         </is>
       </c>
-      <c r="L7" s="24" t="inlineStr">
+      <c r="L9" s="15" t="inlineStr">
         <is>
           <t>北京（GitHub Location: Beijing China）</t>
         </is>
       </c>
-      <c r="M7" s="29" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N7" s="29" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O7" s="30" t="inlineStr">
+      <c r="O9" s="21" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P7" s="24" t="inlineStr">
+      <c r="P9" s="15" t="inlineStr">
         <is>
           <t>GitHub
 v2ex</t>
         </is>
       </c>
-      <c r="Q7" s="24" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="32" t="n"/>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="28" t="inlineStr">
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="19" t="inlineStr">
         <is>
           <t>Nico Hu</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>PH maker（自称 one of the makers of Moli by Lexmount）</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K8" s="29" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>未查到可靠公开履历（同名 LinkedIn 多为生物医药，未核实为同一人）</t>
         </is>
       </c>
-      <c r="L8" s="29" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="M8" s="29" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="N8" s="29" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O8" s="30" t="inlineStr">
+      <c r="O10" s="21" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P8" s="33" t="inlineStr">
+      <c r="P10" s="34" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="Q8" s="33" t="inlineStr">
+      <c r="Q10" s="34" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="106" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+    <row r="11" ht="106" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Agent-Reach</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1386,148 +1572,148 @@
           </r>
         </is>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D11" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E11" s="39" t="n">
         <v>746</v>
       </c>
-      <c r="F9" s="39" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="36" t="inlineStr">
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>10-13/27 #10 +746</t>
         </is>
       </c>
-      <c r="H9" s="40" t="inlineStr">
+      <c r="H11" s="41" t="inlineStr">
         <is>
           <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I9" s="36" t="inlineStr">
+      <c r="I11" s="37" t="inlineStr">
         <is>
           <t>Solo founder / 主要作者与维护者（华人主导：中文 README、foxmail、Bilibili/小红书渠道、UTC+8 活跃）</t>
         </is>
       </c>
-      <c r="J9" s="29" t="inlineStr">
+      <c r="J11" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K9" s="36" t="inlineStr">
+      <c r="K11" s="37" t="inlineStr">
         <is>
           <t>自称 Solo founder（All employees are AI）；主导 Agent-Reach、xfetch 等开源项目；自 2020 年起在 GitHub 活跃</t>
         </is>
       </c>
-      <c r="L9" s="29" t="inlineStr">
+      <c r="L11" s="30" t="inlineStr">
         <is>
           <t>未查到（个人页标注 When I Code UTC+8，不足以定城市）</t>
         </is>
       </c>
-      <c r="M9" s="36" t="inlineStr">
+      <c r="M11" s="37" t="inlineStr">
         <is>
           <t>pnt01@foxmail.com</t>
         </is>
       </c>
-      <c r="N9" s="29" t="inlineStr">
+      <c r="N11" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O9" s="30" t="inlineStr">
+      <c r="O11" s="31" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P9" s="36" t="inlineStr">
+      <c r="P11" s="37" t="inlineStr">
         <is>
           <t>X
 GitHub
 discord</t>
         </is>
       </c>
-      <c r="Q9" s="36" t="inlineStr">
+      <c r="Q11" s="37" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>ziwei-doushu</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>紫微斗数开源排盘引擎（倪海厦《天纪》体系）+ 67.5 万命盘×13 维解读数据集 v4.0；商业站 metisziwei.com</t>
         </is>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D12" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E12" s="43" t="n">
         <v>199</v>
       </c>
-      <c r="F10" s="43" t="inlineStr">
+      <c r="F12" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="36" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>10-25/26 #7 +199</t>
         </is>
       </c>
-      <c r="H10" s="40" t="inlineStr">
+      <c r="H12" s="41" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I10" s="36" t="inlineStr">
+      <c r="I12" s="37" t="inlineStr">
         <is>
           <t>作者 / Metis 创始人，自称一人用 AI 做出商业化 SaaS</t>
         </is>
       </c>
-      <c r="J10" s="29" t="inlineStr">
+      <c r="J12" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="K10" s="36" t="inlineStr">
+      <c r="K12" s="37" t="inlineStr">
         <is>
           <t>Metis紫微创始人；称专业版订阅超 800、注册超 1 万</t>
         </is>
       </c>
-      <c r="L10" s="36" t="inlineStr">
+      <c r="L12" s="37" t="inlineStr">
         <is>
           <t>重庆（运营主体注册地）</t>
         </is>
       </c>
-      <c r="M10" s="36" t="inlineStr">
+      <c r="M12" s="37" t="inlineStr">
         <is>
           <t>wdy778@outlook.com</t>
         </is>
       </c>
-      <c r="N10" s="29" t="inlineStr">
+      <c r="N12" s="30" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="O10" s="30" t="inlineStr">
+      <c r="O12" s="31" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
-      <c r="P10" s="36" t="inlineStr">
+      <c r="P12" s="37" t="inlineStr">
         <is>
           <t>X
 王多鱼AI2.0
@@ -1535,33 +1721,41 @@
 GitHub</t>
         </is>
       </c>
-      <c r="Q10" s="36" t="inlineStr">
+      <c r="Q12" s="37" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q10"/>
-  <mergeCells count="9">
-    <mergeCell ref="F6:F8"/>
+  <autoFilter ref="A3:Q12"/>
+  <mergeCells count="16">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="G8:G10"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="C8:C10"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1686,17 +1880,17 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>总星 36,265，「反 AI 味」设计 skill，给 Claude Code / Cursor / Codex</t>
-        </is>
-      </c>
-      <c r="E4" s="44" t="n">
+          <t>总星 38,959，「反 AI 味」设计 skill</t>
+        </is>
+      </c>
+      <c r="E4" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="45" t="n">
-        <v>3561</v>
+      <c r="F4" s="46" t="n">
+        <v>6391</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>2244</v>
+        <v>2830</v>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
@@ -1705,17 +1899,17 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>10-26 #2 +1,317🚀 → 10-27 #1 +2,244🚀</t>
+          <t>10-26 #2 +1,317🚀 → 10-27 #1 +2,244🚀 → 10-28 #2 +2,830</t>
         </is>
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>Hassan El Mghari</t>
+          <t>Hassan El Mghari，非华人</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Nutlope；非华人</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
@@ -1742,14 +1936,14 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>总星 89,168，让 AI 编程工具更懂设计的设计语言</t>
-        </is>
-      </c>
-      <c r="E5" s="46" t="n">
+          <t>总星 90,483，让 AI 编程工具更懂设计的设计语言</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="45" t="n">
-        <v>2598</v>
+      <c r="F5" s="46" t="n">
+        <v>4047</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>1506</v>
@@ -1761,7 +1955,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506</t>
+          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506 → 10-28 #5 +1,449</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -1798,17 +1992,17 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>总星 6,439，心动出品的开源开箱即用 AI Agent</t>
-        </is>
-      </c>
-      <c r="E6" s="44" t="n">
+          <t>总星 7,445，心动出品的开源开箱即用 AI Agent</t>
+        </is>
+      </c>
+      <c r="E6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="45" t="n">
-        <v>1971</v>
+      <c r="F6" s="46" t="n">
+        <v>3436</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1296</v>
+        <v>1465</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -1817,7 +2011,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀</t>
+          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀 → 10-28 #6 +1,465</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -1839,350 +2033,334 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>🚀 thinkrail</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>开发工具</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>总星 3,971，JetBrains 轻量 Vibe Coding IDE</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>2428</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>1204</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀 → 10-28 #10 +1,204</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>JetBrains 官方</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ECC</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>总星 290,865，Agent harness 性能优化系统</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>2061</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>1165</v>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>10-27 #5 +896 → 10-28 #8 +1,165</t>
+        </is>
+      </c>
+      <c r="J8" s="29" t="inlineStr">
+        <is>
+          <t>Affaan Mustafa，非华人</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>🚀 microduck</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>总星 12,395，迷你双足小鸭机器人 🦆</t>
         </is>
       </c>
-      <c r="E7" s="46" t="n">
+      <c r="E9" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F9" s="46" t="n">
         <v>1490</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G9" s="8" t="n">
         <v>843</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>10-26 #5 +647🚀 → 10-27 #8 +843</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Pollen Robotics</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>法国</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>🚀 thinkrail</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>🚀 postiz-app</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>开发工具</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>总星 2,874，JetBrains 轻量 Vibe Coding IDE（围绕 pi 定制）</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>总星 39,352，开源 agentic 社媒排程工具</t>
+        </is>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>1139</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>951</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>10-27 #12 +188 → 10-28 #7 +951🚀</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Gitroom</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Israel；非华人主导</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>🚀 openbot</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>总星 2,406，本地优先桌面工作区，持久 AI 队友（Codex / Claude / Grok）</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="45" t="n">
-        <v>1224</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>1173</v>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="F11" s="46" t="n">
+        <v>953</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>777</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>JetBrains 官方</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>10-27 #9 +176 → 10-28 #3 +777🚀</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>未发现华人主导</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>ECC</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>jailbreaks</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>安全</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <b val="1"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t>总星 289,824，Agent harness 性能优化系统</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t>：skills / instincts / memory / 安全与研究优先开发</t>
-          </r>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>896</v>
-      </c>
-      <c r="G9" s="47" t="n">
-        <v>896</v>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>总星 5,493，越狱提示词合集</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>902</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>902</v>
+      </c>
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>10-27 #5 +896</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="inlineStr">
-        <is>
-          <t>Affaan Mustafa</t>
-        </is>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>Jump Trading；非华人</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>claude-seo</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>今日 +197 ⭐，总星 20,832，Claude Code 通用 SEO skill（26 子技能 + 19 子智能体）</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" s="48" t="n">
-        <v>197</v>
-      </c>
-      <c r="G10" s="49" t="n">
-        <v>197</v>
-      </c>
-      <c r="H10" s="27" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>10-28 #11 +902</t>
+        </is>
+      </c>
+      <c r="J12" s="29" t="inlineStr">
+        <is>
+          <t>提示词合集，按规则不计</t>
+        </is>
+      </c>
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>10-26 #11 +197</t>
-        </is>
-      </c>
-      <c r="J10" s="28" t="inlineStr">
-        <is>
-          <t>Agrici Daniel，未核实为华人</t>
-        </is>
-      </c>
-      <c r="K10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>postiz-app</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>总星 38,431，开源 agentic 社媒排程工具</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>188</v>
-      </c>
-      <c r="G11" s="47" t="n">
-        <v>188</v>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>10-27 #12 +188</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>Gitroom</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="inlineStr">
-        <is>
-          <t>Israel；非华人主导</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>openbot</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>今日 +176 ⭐，总星 1,457，本地优先桌面工作区，持久 AI 队友（Codex / Claude / Grok）</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F12" s="48" t="n">
-        <v>176</v>
-      </c>
-      <c r="G12" s="49" t="n">
-        <v>176</v>
-      </c>
-      <c r="H12" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>10-27 #9 +176</t>
-        </is>
-      </c>
-      <c r="J12" s="28" t="inlineStr">
-        <is>
-          <t>未发现华人主导</t>
-        </is>
-      </c>
-      <c r="K12" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="L12" s="31" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2191,7 +2369,7 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Strawberry 1.0</t>
+          <t>TheySaid 4.0</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -2206,33 +2384,33 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>内置 AI Companions 的浏览器，替团队干调研 / 跟进 / 行政杂活</t>
-        </is>
-      </c>
-      <c r="E13" s="50" t="n">
+          <t>317 票，在你搭产品的地方直接预演用户反应</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="51" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="51" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="52" t="n">
-        <v>265</v>
+      <c r="H13" s="50" t="n">
+        <v>317</v>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>10-26 #1</t>
+          <t>10-27 #1</t>
         </is>
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>未发现华人主导</t>
+          <t>快速查未发现华人主导</t>
         </is>
       </c>
       <c r="K13" s="15" t="inlineStr">
@@ -2247,58 +2425,58 @@
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Overmind</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>给 Agent 用的最快无头浏览器引擎</t>
-        </is>
-      </c>
-      <c r="E14" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>272 票，开源的持续学习平台</t>
+        </is>
+      </c>
+      <c r="E14" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H14" s="53" t="n">
-        <v>234</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>10-25 #1</t>
-        </is>
-      </c>
-      <c r="J14" s="28" t="inlineStr">
-        <is>
-          <t>昨日华人项，今日跌出 PH 日榜</t>
-        </is>
-      </c>
-      <c r="K14" s="24" t="inlineStr">
+        <v>272</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>10-27 #2</t>
+        </is>
+      </c>
+      <c r="J14" s="29" t="inlineStr">
+        <is>
+          <t>快速查未发现华人主导</t>
+        </is>
+      </c>
+      <c r="K14" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="30" t="inlineStr">
+      <c r="L14" s="31" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2307,7 +2485,7 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>SurgePix</t>
+          <t>Strawberry 1.0</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -2322,28 +2500,28 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>可分层编辑的 AI 视觉工具，也开放 agent skills</t>
-        </is>
-      </c>
-      <c r="E15" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="51" t="inlineStr">
+          <t>内置 AI Companions 的浏览器，替团队干调研 / 跟进 / 行政杂活</t>
+        </is>
+      </c>
+      <c r="E15" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="51" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="52" t="n">
-        <v>212</v>
+      <c r="H15" s="50" t="n">
+        <v>265</v>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>10-26 #2</t>
+          <t>10-26 #1</t>
         </is>
       </c>
       <c r="J15" s="19" t="inlineStr">
@@ -2362,115 +2540,115 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>MiniMax M3.1 Flash</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>MiniMax 新 Flash 模型，号称 agent 场景约快 3×、便宜 70%</t>
-        </is>
-      </c>
-      <c r="E16" s="55" t="n">
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>给 Agent 用的最快无头浏览器引擎</t>
+        </is>
+      </c>
+      <c r="E16" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="53" t="n">
+        <v>234</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>10-25 #1</t>
+        </is>
+      </c>
+      <c r="J16" s="29" t="inlineStr">
+        <is>
+          <t>昨日华人项，今日跌出 PH 日榜</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="35" t="inlineStr">
+        <is>
+          <t>VoiceStudio</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
+        <is>
+          <t>总星 89,187，本地开源 ElevenLabs 替代，语音克隆 / 配音 / 多语种</t>
+        </is>
+      </c>
+      <c r="E17" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F17" s="43" t="n">
+        <v>3889</v>
+      </c>
+      <c r="G17" s="55" t="n">
+        <v>2297</v>
+      </c>
+      <c r="H17" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="I17" s="37" t="inlineStr">
+        <is>
+          <t>10-18/26 #3 +1,592 → 10-27 #11 +2,297</t>
+        </is>
+      </c>
+      <c r="J17" s="41" t="inlineStr">
+        <is>
+          <t>Deb Palash，未核实为华人</t>
+        </is>
+      </c>
+      <c r="K17" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="53" t="n">
-        <v>171</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>10-26 #3</t>
-        </is>
-      </c>
-      <c r="J16" s="28" t="inlineStr">
-        <is>
-          <t>MiniMax 大厂官方模型发布，不计独立华人项目</t>
-        </is>
-      </c>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>VoiceStudio</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="inlineStr">
-        <is>
-          <t>总星 89,187，本地开源 ElevenLabs 替代，语音克隆 / 配音 / 多语种</t>
-        </is>
-      </c>
-      <c r="E17" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="38" t="n">
-        <v>3889</v>
-      </c>
-      <c r="G17" s="57" t="n">
-        <v>2297</v>
-      </c>
-      <c r="H17" s="39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="36" t="inlineStr">
-        <is>
-          <t>10-18/26 #3 +1,592 → 10-27 #11 +2,297</t>
-        </is>
-      </c>
-      <c r="J17" s="40" t="inlineStr">
-        <is>
-          <t>Deb Palash，未核实为华人</t>
-        </is>
-      </c>
-      <c r="K17" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="30" t="inlineStr">
+      <c r="L17" s="31" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2518,92 +2696,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="58" t="inlineStr">
+      <c r="B1" s="56" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-26 – 11-01）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="59" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 5 个 · 核心人物 7 位</t>
+      <c r="B2" s="57" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 6 个 · 核心人物 9 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="62" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-27（第 2/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-28（第 3/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="62" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 debpalash/VoiceStudio；已收录全球项目 14 个、华人项目 5 个，今日新增华人项目：alchaincyf/huashu-design、Panniantong/Agent-Reach。</t>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 Nutlope/hallmark；已收录全球项目 14 个、华人项目 6 个，今日新增华人项目：HKUDS/DeepTutor。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="62" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="63" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="64" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="65" t="inlineStr">
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="66" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="67" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-11-01/</t>
         </is>
@@ -2624,7 +2802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2676,27 +2854,27 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="66" t="inlineStr">
         <is>
           <t>https://github.com/Yijia-Xiao</t>
         </is>
@@ -2723,34 +2901,34 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E5" s="68" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>https://yijia-xiao.com/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>https://github.com/TauricResearch/TradingAgents</t>
         </is>
@@ -2777,414 +2955,414 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E7" s="68" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>https://tauric.ai/contact/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="66" t="inlineStr">
         <is>
           <t>https://tauric.ai/research/tradingagents</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="50" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>https://bingxi.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E10" s="66" t="inlineStr">
+        <is>
+          <t>https://github.com/pancacake</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.26962</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E12" s="66" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/chaoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>GitHub 组织</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/HKUDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="inlineStr">
+        <is>
+          <t>https://datascience.hku.hk/people/chao-huang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.26962</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E9" s="68" t="inlineStr">
+      <c r="E16" s="66" t="inlineStr">
         <is>
           <t>https://x.com/AlchainHust</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E11" s="68" t="inlineStr">
+      <c r="E18" s="66" t="inlineStr">
         <is>
           <t>https://github.com/alchaincyf</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/insights/wechat-2247485096-1/</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E13" s="68" t="inlineStr">
+      <c r="E20" s="66" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/consulting/</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+    <row r="21" ht="50" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>来源5</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E21" s="34" t="inlineStr">
         <is>
           <t>https://github.com/alchaincyf/huashu-design</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>来源6</t>
         </is>
       </c>
-      <c r="E15" s="68" t="inlineStr">
+      <c r="E22" s="66" t="inlineStr">
         <is>
           <t>https://m.okjike.com/users/27BF807A-FA4D-4B01-AAFD-05FAAA674335</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E16" s="33" t="inlineStr">
-        <is>
-          <t>https://wenjiai.cn/products/lanyue-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E17" s="68" t="inlineStr">
-        <is>
-          <t>https://vc.pedaily.cn/company/865282.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E18" s="33" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/about</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E19" s="68" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/privacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>来源5</t>
-        </is>
-      </c>
-      <c r="E20" s="33" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E21" s="68" t="inlineStr">
-        <is>
-          <t>https://github.com/ldm0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>v2ex</t>
-        </is>
-      </c>
-      <c r="E22" s="33" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1236833</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3374,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Donough Liu（GitHub ldm0）</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -3206,39 +3384,39 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>https://wenjiai.cn/products/lanyue-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E23" s="68" t="inlineStr">
-        <is>
-          <t>https://github.com/lexmount/moli</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E24" s="33" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
+      <c r="E24" s="66" t="inlineStr">
+        <is>
+          <t>https://vc.pedaily.cn/company/865282.html</t>
         </is>
       </c>
     </row>
@@ -3250,351 +3428,540 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/about</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E26" s="66" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>来源5</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E28" s="66" t="inlineStr">
+        <is>
+          <t>https://github.com/ldm0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>v2ex</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1236833</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E30" s="66" t="inlineStr">
+        <is>
+          <t>https://github.com/lexmount/moli</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
           <t>Nico Hu</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E25" s="68" t="inlineStr">
+      <c r="E32" s="66" t="inlineStr">
         <is>
           <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Nico Hu</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E26" s="33" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E27" s="68" t="inlineStr">
-        <is>
-          <t>https://x.com/Neo_Reidlab</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="64" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E28" s="33" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>discord</t>
-        </is>
-      </c>
-      <c r="E29" s="68" t="inlineStr">
-        <is>
-          <t>https://discord.gg/NSZz22R39</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="64" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E31" s="68" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="64" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E32" s="33" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Nico Hu</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E34" s="66" t="inlineStr">
+        <is>
+          <t>https://x.com/Neo_Reidlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>discord</t>
+        </is>
+      </c>
+      <c r="E36" s="66" t="inlineStr">
+        <is>
+          <t>https://discord.gg/NSZz22R39</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="29" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E38" s="66" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E39" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D40" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E33" s="68" t="inlineStr">
+      <c r="E40" s="66" t="inlineStr">
         <is>
           <t>https://x.com/wdy188</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E34" s="33" t="inlineStr">
+      <c r="E41" s="34" t="inlineStr">
         <is>
           <t>https://github.com/Renhuai123</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D42" s="25" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E35" s="68" t="inlineStr">
+      <c r="E42" s="66" t="inlineStr">
         <is>
           <t>https://github.com/Renhuai123/ziwei-doushu</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E36" s="33" t="inlineStr">
+      <c r="E43" s="34" t="inlineStr">
         <is>
           <t>https://metisziwei.com/privacy</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B44" s="25" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E37" s="68" t="inlineStr">
+      <c r="E44" s="66" t="inlineStr">
         <is>
           <t>https://zamantika.com/profile/wdy188</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E37"/>
+  <autoFilter ref="A3:E44"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -3634,6 +4001,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId41"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-11-01/weekly-2026-11-01.xlsx
+++ b/2026-11-01/weekly-2026-11-01.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,9 +31,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;#&quot;0"/>
-    <numFmt numFmtId="165" formatCode="+#,##0&quot; 🚀&quot;"/>
+    <numFmt numFmtId="165" formatCode="+#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot; ★&quot;"/>
-    <numFmt numFmtId="167" formatCode="+#,##0"/>
+    <numFmt numFmtId="167" formatCode="+#,##0&quot; 🚀&quot;"/>
     <numFmt numFmtId="168" formatCode="&quot;PH #&quot;0"/>
     <numFmt numFmtId="169" formatCode="#,##0&quot; 票&quot;"/>
   </numFmts>
@@ -230,6 +230,34 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -242,7 +270,7 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,7 +297,7 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -284,39 +312,11 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -328,58 +328,58 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -396,7 +396,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -764,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -887,54 +887,246 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="106" customHeight="1">
+    <row r="4" ht="92" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>DeepTutor</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>港大 HKUDS 开源的 agent 原生个性化 AI 家教</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：引用溯源解题辅导 + 按难度出题 + 学习者记忆闭环</t>
+          </r>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>3969</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>10-28 #9 +1,598 → 10-29 #4 +2,371</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>主要作者（GitHub pancacake，贡献居首）、论文共同一作</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>北京交通大学电子与通信工程本科（2023–2027 预计）；北大附中（2017–2023）；港大计算与数据科学学院 Year-0 博士（导师黄超）</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>港大</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve"> Data Intelligence Lab 研究助理；中科院自动化所 3DV Lab、清华 AIR、Lancaster 大学（远程）、北交大软件学院实习；另发布 CatchMe</t>
+          </r>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>北京 / 香港（就读地，常住城市未查到）</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>个人站
+GitHub</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>HKUDS 负责人、论文通讯作者</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>University of Notre Dame 计算机博士</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>港大</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>计算机系与数据科学学院助理教授；带队 LightRAG、CLI-Anything 等</t>
+          </r>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>香港</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>chuang@cs.hku.hk</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>个人站
+GitHub 组织</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="106" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
           <t>🚀 TradingAgents</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>多智能体编排</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>多智能体 LLM 金融交易框架，模拟投行式分工（分析师→交易员→风控）；配套 Trading-R1 等；Tauric Research 创始人独立研究项目</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D6" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E6" s="18" t="n">
         <v>1776</v>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>10-26 #6 +381 → 10-27 #2 +1,395🚀</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>Tauric Research 创始人；TradingAgents 第一作者 / 主要贡献者</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>清华大学计算机学士（2018–2022，导师唐杰）；UCLA 计算机博士在读（2022–，导师 Wei Wang；主页写 fourth-year Ph.D. candidate）</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -963,243 +1155,51 @@
           </r>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>洛杉矶（UCLA）</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>yijia.xiao@cs.ucla.edu
 contact@tauric.ai</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr">
         <is>
           <t>GitHub
 个人站</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q6" s="16" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>DeepTutor</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
+    <row r="7" ht="148" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>huashu-design</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <b val="1"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t>港大 HKUDS 开源的 agent 原生个性化 AI 家教</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t>：引用溯源解题辅导 + 按难度出题 + 学习者记忆闭环</t>
-          </r>
-        </is>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>1598</v>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>10-28 #9 +1,598</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
-        <is>
-          <t>Bingxi Zhao（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>主要作者（GitHub pancacake，贡献居首）、论文共同一作</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>北京交通大学电子与通信工程本科（2023–2027 预计）；北大附中（2017–2023）；港大计算与数据科学学院 Year-0 博士（导师黄超）</t>
-        </is>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <b val="1"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t>港大</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve"> Data Intelligence Lab 研究助理；中科院自动化所 3DV Lab、清华 AIR、Lancaster 大学（远程）、北交大软件学院实习；另发布 CatchMe</t>
-          </r>
-        </is>
-      </c>
-      <c r="L5" s="15" t="inlineStr">
-        <is>
-          <t>北京 / 香港（就读地，常住城市未查到）</t>
-        </is>
-      </c>
-      <c r="M5" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O5" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P5" s="15" t="inlineStr">
-        <is>
-          <t>个人站
-GitHub</t>
-        </is>
-      </c>
-      <c r="Q5" s="15" t="inlineStr">
-        <is>
-          <t>来源1、来源2、来源3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="22" t="n"/>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="E6" s="22" t="n"/>
-      <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>HKUDS 负责人、论文通讯作者</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>University of Notre Dame 计算机博士</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <b val="1"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t>港大</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="微软雅黑"/>
-              <color rgb="001F2937"/>
-              <sz val="10"/>
-            </rPr>
-            <t>计算机系与数据科学学院助理教授；带队 LightRAG、CLI-Anything 等</t>
-          </r>
-        </is>
-      </c>
-      <c r="L6" s="15" t="inlineStr">
-        <is>
-          <t>香港</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>chuang@cs.hku.hk</t>
-        </is>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O6" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P6" s="15" t="inlineStr">
-        <is>
-          <t>个人站
-GitHub 组织</t>
-        </is>
-      </c>
-      <c r="Q6" s="15" t="inlineStr">
-        <is>
-          <t>来源1、来源2、来源3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="148" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>huashu-design</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1220,38 +1220,38 @@
           </r>
         </is>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="8" t="n">
         <v>251</v>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>10-27 #13 +251</t>
         </is>
       </c>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>作者 / 独立开发者；huashu-design、nuwa-skill 等开源 skill 作者</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>华中科技大学经济学专业（理科）本科</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1280,27 +1280,27 @@
           </r>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>China（GitHub location）；小红书 IP 属地显示云南；固定定居城市未查到（自述近年多国旅居）</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>alchaincyf@gmail.com</t>
         </is>
       </c>
-      <c r="N7" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P7" s="25" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>X
 alchain
@@ -1312,24 +1312,125 @@
 花叔（只工作不上班版）</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5、来源6</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>the-craft-of-selfteaching</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>《自学是门手艺》</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：以 Python 为例讲如何自学的开源书（Jupyter Notebook，2019 年创建）</t>
+          </r>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>10-29 #14 +148</t>
+        </is>
+      </c>
+      <c r="H8" s="29" t="inlineStr">
+        <is>
+          <t>李笑来（xiaolai）</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>长春大学会计学专业</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr">
+        <is>
+          <t>原新东方国外部高级教师（2001–2008）；2008 年创立艾德睿智国际教育咨询；2013 年创立比特基金，INBlockchain 硬币资本创始人；著《把时间当作朋友》《财富自由之路》等</t>
+        </is>
+      </c>
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t>北京（GitHub 资料）</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>lixiaolai@gmail.com</t>
+        </is>
+      </c>
+      <c r="N8" s="30" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O8" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P8" s="25" t="inlineStr">
+        <is>
+          <t>X
+个人站
+GitHub</t>
+        </is>
+      </c>
+      <c r="Q8" s="25" t="inlineStr">
+        <is>
+          <t>来源1、来源2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1350,208 +1451,308 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>深圳市揽岳智能科技有限公司法定代表人、董事长兼经理</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>未查到（公开报道多写柔宇联合创始人为清华/斯坦福校友群体，未单独证实其学历）</t>
         </is>
       </c>
-      <c r="K8" s="15" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>柔宇科技联合创始人之一、曾任副总裁（与刘自鸿、魏鹏等）；2025 转向 AI 云端浏览器基础设施创业，创立揽岳智能 / Lexmount</t>
         </is>
       </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>深圳（公司注册地）；北京亦有运营主体</t>
         </is>
       </c>
-      <c r="M8" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O8" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P8" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q8" s="15" t="inlineStr">
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="33" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="19" t="inlineStr">
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="33" t="n"/>
+      <c r="B10" s="33" t="n"/>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+      <c r="G10" s="33" t="n"/>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Moli 核心开发者 / PH maker；lexmount/moli 主要贡献者</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>北京开发者；在创业公司做浏览器相关，主导开源 Moli；V2EX 发帖介绍项目</t>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>北京（GitHub Location: Beijing China）</t>
         </is>
       </c>
-      <c r="M9" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N9" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O9" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P9" s="15" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>GitHub
 v2ex</t>
         </is>
       </c>
-      <c r="Q9" s="15" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="19" t="inlineStr">
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Nico Hu</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>PH maker（自称 one of the makers of Moli by Lexmount）</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>未查到可靠公开履历（同名 LinkedIn 多为生物医药，未核实为同一人）</t>
         </is>
       </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O10" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P10" s="34" t="inlineStr">
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P11" s="34" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="Q10" s="34" t="inlineStr">
+      <c r="Q11" s="34" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="106" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>LinkSwift</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>工具</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="00A0A0A0"/>
+              <sz val="10"/>
+            </rPr>
+            <t>油猴脚本</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="00A0A0A0"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：获取百度/阿里/夸克/天翼/123 等八大网盘文件直链，基于「网盘直链下载助手」修改</t>
+          </r>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>10-18/29 #11 +1,616</t>
+        </is>
+      </c>
+      <c r="H12" s="41" t="inlineStr">
+        <is>
+          <t>Hmjz100（真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>作者，GitHub 贡献 326 次，几乎独立维护</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K12" s="37" t="inlineStr">
+        <is>
+          <t>GitHub 简介自称独立开发者；资料中公司/城市为虚构（虚拟学院、虚拟城）</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P12" s="37" t="inlineStr">
+        <is>
+          <t>GitHub
+博客</t>
+        </is>
+      </c>
+      <c r="Q12" s="37" t="inlineStr">
+        <is>
+          <t>来源1、来源2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="106" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Agent-Reach</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1572,148 +1773,148 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D13" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E13" s="43" t="n">
         <v>746</v>
       </c>
-      <c r="F11" s="40" t="inlineStr">
+      <c r="F13" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>10-13/27 #10 +746</t>
         </is>
       </c>
-      <c r="H11" s="41" t="inlineStr">
+      <c r="H13" s="41" t="inlineStr">
         <is>
           <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I11" s="37" t="inlineStr">
+      <c r="I13" s="37" t="inlineStr">
         <is>
           <t>Solo founder / 主要作者与维护者（华人主导：中文 README、foxmail、Bilibili/小红书渠道、UTC+8 活跃）</t>
         </is>
       </c>
-      <c r="J11" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K11" s="37" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K13" s="37" t="inlineStr">
         <is>
           <t>自称 Solo founder（All employees are AI）；主导 Agent-Reach、xfetch 等开源项目；自 2020 年起在 GitHub 活跃</t>
         </is>
       </c>
-      <c r="L11" s="30" t="inlineStr">
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>未查到（个人页标注 When I Code UTC+8，不足以定城市）</t>
         </is>
       </c>
-      <c r="M11" s="37" t="inlineStr">
+      <c r="M13" s="37" t="inlineStr">
         <is>
           <t>pnt01@foxmail.com</t>
         </is>
       </c>
-      <c r="N11" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O11" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P11" s="37" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P13" s="37" t="inlineStr">
         <is>
           <t>X
 GitHub
 discord</t>
         </is>
       </c>
-      <c r="Q11" s="37" t="inlineStr">
+      <c r="Q13" s="37" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>ziwei-doushu</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>紫微斗数开源排盘引擎（倪海厦《天纪》体系）+ 67.5 万命盘×13 维解读数据集 v4.0；商业站 metisziwei.com</t>
         </is>
       </c>
-      <c r="D12" s="42" t="n">
+      <c r="D14" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="43" t="n">
+      <c r="E14" s="39" t="n">
         <v>199</v>
       </c>
-      <c r="F12" s="44" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>10-25/26 #7 +199</t>
         </is>
       </c>
-      <c r="H12" s="41" t="inlineStr">
+      <c r="H14" s="41" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I12" s="37" t="inlineStr">
+      <c r="I14" s="37" t="inlineStr">
         <is>
           <t>作者 / Metis 创始人，自称一人用 AI 做出商业化 SaaS</t>
         </is>
       </c>
-      <c r="J12" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K12" s="37" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K14" s="37" t="inlineStr">
         <is>
           <t>Metis紫微创始人；称专业版订阅超 800、注册超 1 万</t>
         </is>
       </c>
-      <c r="L12" s="37" t="inlineStr">
+      <c r="L14" s="37" t="inlineStr">
         <is>
           <t>重庆（运营主体注册地）</t>
         </is>
       </c>
-      <c r="M12" s="37" t="inlineStr">
+      <c r="M14" s="37" t="inlineStr">
         <is>
           <t>wdy778@outlook.com</t>
         </is>
       </c>
-      <c r="N12" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O12" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P12" s="37" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P14" s="37" t="inlineStr">
         <is>
           <t>X
 王多鱼AI2.0
@@ -1721,41 +1922,43 @@
 GitHub</t>
         </is>
       </c>
-      <c r="Q12" s="37" t="inlineStr">
+      <c r="Q14" s="37" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q12"/>
+  <autoFilter ref="A3:Q14"/>
   <mergeCells count="16">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="D9:D11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1862,527 +2065,527 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>🚀 hallmark</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>总星 38,959，「反 AI 味」设计 skill</t>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>总星 40,678，「反 AI 味」设计 skill</t>
         </is>
       </c>
       <c r="E4" s="45" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="46" t="n">
-        <v>6391</v>
-      </c>
-      <c r="G4" s="8" t="n">
+        <v>8501</v>
+      </c>
+      <c r="G4" s="18" t="n">
         <v>2830</v>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>10-26 #2 +1,317🚀 → 10-27 #1 +2,244🚀 → 10-28 #2 +2,830</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>Hassan El Mghari，非华人</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>10-26 #2 +1,317🚀 → 10-27 #1 +2,244🚀 → 10-28 #2 +2,830 → 10-29 #6 +2,110</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>非华人</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>🚀 impeccable</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>总星 90,483，让 AI 编程工具更懂设计的设计语言</t>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>总星 92,607，给编程 agent 的设计词汇表</t>
         </is>
       </c>
       <c r="E5" s="47" t="n">
         <v>4</v>
       </c>
       <c r="F5" s="46" t="n">
-        <v>4047</v>
-      </c>
-      <c r="G5" s="8" t="n">
+        <v>5519</v>
+      </c>
+      <c r="G5" s="18" t="n">
         <v>1506</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506 → 10-28 #5 +1,449</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>Paul Bakaus</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506 → 10-28 #5 +1,449 → 10-29 #7 +1,472</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>非华人</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>🚀 cindy</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>总星 7,445，心动出品的开源开箱即用 AI Agent</t>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>总星 8,085，心动出品的开源 AI Agent</t>
         </is>
       </c>
       <c r="E6" s="45" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="46" t="n">
-        <v>3436</v>
-      </c>
-      <c r="G6" s="8" t="n">
+        <v>4164</v>
+      </c>
+      <c r="G6" s="18" t="n">
         <v>1465</v>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀 → 10-28 #6 +1,465</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀 → 10-28 #6 +1,465 → 10-29 #8 +728</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>心动网络</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>XD；官方项目，不计独立</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>🚀 thinkrail</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>开发工具</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>总星 3,971，JetBrains 轻量 Vibe Coding IDE</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>总星 5,017，JetBrains 轻量 Vibe Coding IDE</t>
+        </is>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>3496</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>1204</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀 → 10-28 #10 +1,204 → 10-29 #1 +1,068</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>JetBrains 官方</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>🚀 jailbreaks</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>总星 7,079，越狱提示词合集</t>
+        </is>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="46" t="n">
+        <v>2379</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>1477</v>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>10-28 #11 +902 → 10-29 #10 +1,477🚀</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>提示词合集，按规则不计</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>ECC</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>总星 290,865，Agent harness 性能优化系统</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>2061</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>1165</v>
+      </c>
+      <c r="H9" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>10-27 #5 +896 → 10-28 #8 +1,165</t>
+        </is>
+      </c>
+      <c r="J9" s="29" t="inlineStr">
+        <is>
+          <t>Affaan Mustafa，非华人</t>
+        </is>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>🚀 openbot</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>总星 3,235，本地优先的持久 AI 队友桌面工作区</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="46" t="n">
-        <v>2428</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>1204</v>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="F10" s="46" t="n">
+        <v>2007</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>1054</v>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀 → 10-28 #10 +1,204</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>JetBrains 官方</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>10-27 #9 +176 → 10-28 #3 +777🚀 → 10-29 #9 +1,054</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>未发现华人主导</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>ECC</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>🚀 superpowers</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>总星 290,865，Agent harness 性能优化系统</t>
-        </is>
-      </c>
-      <c r="E8" s="26" t="n">
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>总星 307,428，agentic skills 框架 + 开发方法论</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="46" t="n">
+        <v>1712</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>10-28 #4 +617 → 10-29 #3 +1,095🚀</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>非华人</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="22" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>🚀 microduck</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>总星 12,395，迷你双足小鸭机器人 🦆</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="27" t="n">
-        <v>2061</v>
-      </c>
-      <c r="G8" s="48" t="n">
-        <v>1165</v>
-      </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="F12" s="46" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>843</v>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
-        <is>
-          <t>10-27 #5 +896 → 10-28 #8 +1,165</t>
-        </is>
-      </c>
-      <c r="J8" s="29" t="inlineStr">
-        <is>
-          <t>Affaan Mustafa，非华人</t>
-        </is>
-      </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>10-26 #5 +647🚀 → 10-27 #8 +843</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>Pollen Robotics</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>🚀 microduck</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>TheySaid 4.0</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>总星 12,395，迷你双足小鸭机器人 🦆</t>
-        </is>
-      </c>
-      <c r="E9" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="46" t="n">
-        <v>1490</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>843</v>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>10-26 #5 +647🚀 → 10-27 #8 +843</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>Pollen Robotics</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>法国</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>🚀 postiz-app</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>总星 39,352，开源 agentic 社媒排程工具</t>
-        </is>
-      </c>
-      <c r="E10" s="47" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <v>1139</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>951</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>10-27 #12 +188 → 10-28 #7 +951🚀</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Gitroom</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>Israel；非华人主导</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>🚀 openbot</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>总星 2,406，本地优先桌面工作区，持久 AI 队友（Codex / Claude / Grok）</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="46" t="n">
-        <v>953</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>777</v>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>10-27 #9 +176 → 10-28 #3 +777🚀</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>未发现华人主导</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>jailbreaks</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>总星 5,493，越狱提示词合集</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>902</v>
-      </c>
-      <c r="G12" s="48" t="n">
-        <v>902</v>
-      </c>
-      <c r="H12" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="25" t="inlineStr">
-        <is>
-          <t>10-28 #11 +902</t>
-        </is>
-      </c>
-      <c r="J12" s="29" t="inlineStr">
-        <is>
-          <t>提示词合集，按规则不计</t>
-        </is>
-      </c>
-      <c r="K12" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>TheySaid 4.0</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>317 票，在你搭产品的地方直接预演用户反应</t>
         </is>
@@ -2390,70 +2593,70 @@
       <c r="E13" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="G13" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="50" t="n">
+      <c r="H13" s="51" t="n">
         <v>317</v>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t>10-27 #1</t>
         </is>
       </c>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="J13" s="29" t="inlineStr">
         <is>
           <t>快速查未发现华人主导</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="L13" s="31" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Overmind</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>272 票，开源的持续学习平台</t>
         </is>
       </c>
-      <c r="E14" s="51" t="n">
+      <c r="E14" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="52" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="52" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2461,44 +2664,44 @@
       <c r="H14" s="53" t="n">
         <v>272</v>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>10-27 #2</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>快速查未发现华人主导</t>
         </is>
       </c>
-      <c r="K14" s="25" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="31" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Strawberry 1.0</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>内置 AI Companions 的浏览器，替团队干调研 / 跟进 / 行政杂活</t>
         </is>
@@ -2506,93 +2709,93 @@
       <c r="E15" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr">
+      <c r="G15" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="50" t="n">
+      <c r="H15" s="51" t="n">
         <v>265</v>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>10-26 #1</t>
         </is>
       </c>
-      <c r="J15" s="19" t="inlineStr">
+      <c r="J15" s="29" t="inlineStr">
         <is>
           <t>未发现华人主导</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K15" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="L15" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Dedica</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>给 Agent 用的最快无头浏览器引擎</t>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>测你的网站能不能被 AI agent 用（文案点名 Muse、Instinct、GrokBot），125 项免费检查</t>
         </is>
       </c>
       <c r="E16" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="52" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="52" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H16" s="53" t="n">
-        <v>234</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>10-25 #1</t>
-        </is>
-      </c>
-      <c r="J16" s="29" t="inlineStr">
-        <is>
-          <t>昨日华人项，今日跌出 PH 日榜</t>
-        </is>
-      </c>
-      <c r="K16" s="25" t="inlineStr">
+        <v>261</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>10-28 #1</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="31" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2622,13 +2825,13 @@
       <c r="E17" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="43" t="n">
+      <c r="F17" s="39" t="n">
         <v>3889</v>
       </c>
       <c r="G17" s="55" t="n">
         <v>2297</v>
       </c>
-      <c r="H17" s="44" t="inlineStr">
+      <c r="H17" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2648,7 +2851,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="31" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2705,7 +2908,7 @@
     <row r="2">
       <c r="B2" s="57" t="inlineStr">
         <is>
-          <t>全球项目 14 个 · 华人项目 6 个 · 核心人物 9 位</t>
+          <t>全球项目 14 个 · 华人项目 8 个 · 核心人物 11 位</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2927,7 @@
       </c>
       <c r="B5" s="60" t="inlineStr">
         <is>
-          <t>本周进行中 · 已更新至 10-28（第 3/7 天），每天日报后自动刷新。</t>
+          <t>本周进行中 · 已更新至 10-29（第 4/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2939,7 @@
       </c>
       <c r="B6" s="60" t="inlineStr">
         <is>
-          <t>本周 GitHub 累计星增第一是 Nutlope/hallmark；已收录全球项目 14 个、华人项目 6 个，今日新增华人项目：HKUDS/DeepTutor。</t>
+          <t>本周 GitHub 累计星增第一是 Nutlope/hallmark；已收录全球项目 14 个、华人项目 8 个，今日新增华人项目：hmjz100/LinkSwift、xiaolai/the-craft-of-selfteaching。</t>
         </is>
       </c>
     </row>
@@ -2802,7 +3005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2854,1114 +3057,1303 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>https://bingxi.life/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="inlineStr">
+        <is>
+          <t>https://github.com/pancacake</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Bingxi Zhao（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.26962</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/chaoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>GitHub 组织</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/HKUDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="inlineStr">
+        <is>
+          <t>https://datascience.hku.hk/people/chao-huang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>HKUDS/DeepTutor</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Huang Chao（黄超）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.26962</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E4" s="66" t="inlineStr">
+      <c r="E11" s="66" t="inlineStr">
         <is>
           <t>https://github.com/Yijia-Xiao</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>https://yijia-xiao.com/</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E6" s="66" t="inlineStr">
+      <c r="E13" s="66" t="inlineStr">
         <is>
           <t>https://github.com/TauricResearch/TradingAgents</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>https://tauric.ai/contact/</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E8" s="66" t="inlineStr">
+      <c r="E15" s="66" t="inlineStr">
         <is>
           <t>https://tauric.ai/research/tradingagents</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>HKUDS/DeepTutor</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Bingxi Zhao（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
+        <is>
+          <t>https://x.com/AlchainHust</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
-        <is>
-          <t>https://bingxi.life/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>HKUDS/DeepTutor</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>Bingxi Zhao（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="E17" s="66" t="inlineStr">
+        <is>
+          <t>https://www.huasheng.ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E10" s="66" t="inlineStr">
-        <is>
-          <t>https://github.com/pancacake</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>HKUDS/DeepTutor</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Bingxi Zhao（中文名未查到）</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/alchaincyf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E19" s="66" t="inlineStr">
+        <is>
+          <t>https://www.huasheng.ai/insights/wechat-2247485096-1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.26962</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>HKUDS/DeepTutor</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>https://www.huasheng.ai/consulting/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="50" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>来源5</t>
+        </is>
+      </c>
+      <c r="E21" s="66" t="inlineStr">
+        <is>
+          <t>https://github.com/alchaincyf/huashu-design</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>alchaincyf/huashu-design</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>来源6</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>https://m.okjike.com/users/27BF807A-FA4D-4B01-AAFD-05FAAA674335</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>xiaolai/the-craft-of-selfteaching</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>李笑来（xiaolai）</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="66" t="inlineStr">
+        <is>
+          <t>https://x.com/xiaolai</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>xiaolai/the-craft-of-selfteaching</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>李笑来（xiaolai）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E12" s="66" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/view/chaoh</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>HKUDS/DeepTutor</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="E24" s="34" t="inlineStr">
+        <is>
+          <t>http://lixiaolai.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>xiaolai/the-craft-of-selfteaching</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>李笑来（xiaolai）</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>GitHub 组织</t>
-        </is>
-      </c>
-      <c r="E13" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/HKUDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>HKUDS/DeepTutor</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E25" s="66" t="inlineStr">
+        <is>
+          <t>https://github.com/xiaolai</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>xiaolai/the-craft-of-selfteaching</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>李笑来（xiaolai）</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="inlineStr">
+        <is>
+          <t>https://zh.wikipedia.org/wiki/%E6%9D%8E%E7%AC%91%E6%9D%A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E14" s="66" t="inlineStr">
-        <is>
-          <t>https://datascience.hku.hk/people/chao-huang/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>HKUDS/DeepTutor</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Huang Chao（黄超）</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="E27" s="66" t="inlineStr">
+        <is>
+          <t>https://wenjiai.cn/products/lanyue-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t>https://vc.pedaily.cn/company/865282.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
-        <is>
-          <t>https://arxiv.org/abs/2604.26962</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>alchaincyf/huashu-design</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="E29" s="66" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/about</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>樊俊超</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>来源5</t>
+        </is>
+      </c>
+      <c r="E31" s="66" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E32" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/ldm0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>v2ex</t>
+        </is>
+      </c>
+      <c r="E33" s="66" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1236833</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E34" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/lexmount/moli</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Donough Liu（GitHub ldm0）</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E35" s="66" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Nico Hu</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E36" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="29" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>Nico Hu</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E37" s="66" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>hmjz100/LinkSwift</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Hmjz100（真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E38" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/hmjz100</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>hmjz100/LinkSwift</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>Hmjz100（真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>博客</t>
+        </is>
+      </c>
+      <c r="E39" s="66" t="inlineStr">
+        <is>
+          <t>https://hmjz100blog.rf.gd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>hmjz100/LinkSwift</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Hmjz100（真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E40" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/hmjz100/LinkSwift</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E16" s="66" t="inlineStr">
-        <is>
-          <t>https://x.com/AlchainHust</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>alchaincyf/huashu-design</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="E41" s="66" t="inlineStr">
+        <is>
+          <t>https://x.com/Neo_Reidlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E17" s="34" t="inlineStr">
-        <is>
-          <t>https://www.huasheng.ai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>alchaincyf/huashu-design</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E42" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>discord</t>
+        </is>
+      </c>
+      <c r="E43" s="66" t="inlineStr">
+        <is>
+          <t>https://discord.gg/NSZz22R39</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E44" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="29" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E45" s="66" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E47" s="66" t="inlineStr">
+        <is>
+          <t>https://x.com/wdy188</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E18" s="66" t="inlineStr">
-        <is>
-          <t>https://github.com/alchaincyf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>alchaincyf/huashu-design</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="E48" s="34" t="inlineStr">
+        <is>
+          <t>https://github.com/Renhuai123</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D49" s="25" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
-        <is>
-          <t>https://www.huasheng.ai/insights/wechat-2247485096-1/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
-        <is>
-          <t>alchaincyf/huashu-design</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="E49" s="66" t="inlineStr">
+        <is>
+          <t>https://github.com/Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E20" s="66" t="inlineStr">
-        <is>
-          <t>https://www.huasheng.ai/consulting/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="50" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>alchaincyf/huashu-design</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="E50" s="34" t="inlineStr">
+        <is>
+          <t>https://metisziwei.com/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>来源5</t>
-        </is>
-      </c>
-      <c r="E21" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/alchaincyf/huashu-design</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="50" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>alchaincyf/huashu-design</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>来源6</t>
-        </is>
-      </c>
-      <c r="E22" s="66" t="inlineStr">
-        <is>
-          <t>https://m.okjike.com/users/27BF807A-FA4D-4B01-AAFD-05FAAA674335</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E23" s="34" t="inlineStr">
-        <is>
-          <t>https://wenjiai.cn/products/lanyue-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E24" s="66" t="inlineStr">
-        <is>
-          <t>https://vc.pedaily.cn/company/865282.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/about</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D51" s="25" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E26" s="66" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/privacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>樊俊超</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>来源5</t>
-        </is>
-      </c>
-      <c r="E27" s="34" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E28" s="66" t="inlineStr">
-        <is>
-          <t>https://github.com/ldm0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>v2ex</t>
-        </is>
-      </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1236833</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="29" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E30" s="66" t="inlineStr">
-        <is>
-          <t>https://github.com/lexmount/moli</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E31" s="34" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="29" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>Nico Hu</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E32" s="66" t="inlineStr">
-        <is>
-          <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Nico Hu</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="64" customHeight="1">
-      <c r="A34" s="29" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E34" s="66" t="inlineStr">
-        <is>
-          <t>https://x.com/Neo_Reidlab</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="64" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E35" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="64" customHeight="1">
-      <c r="A36" s="29" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="inlineStr">
-        <is>
-          <t>discord</t>
-        </is>
-      </c>
-      <c r="E36" s="66" t="inlineStr">
-        <is>
-          <t>https://discord.gg/NSZz22R39</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="64" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E37" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="29" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D38" s="25" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E38" s="66" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="64" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E39" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E40" s="66" t="inlineStr">
-        <is>
-          <t>https://x.com/wdy188</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E41" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/Renhuai123</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="29" t="inlineStr">
-        <is>
-          <t>Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D42" s="25" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E42" s="66" t="inlineStr">
-        <is>
-          <t>https://github.com/Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E43" s="34" t="inlineStr">
-        <is>
-          <t>https://metisziwei.com/privacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>Renhuai123/ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E44" s="66" t="inlineStr">
+      <c r="E51" s="66" t="inlineStr">
         <is>
           <t>https://zamantika.com/profile/wdy188</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E44"/>
+  <autoFilter ref="A3:E51"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -4008,6 +4400,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId48"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-11-01/weekly-2026-11-01.xlsx
+++ b/2026-11-01/weekly-2026-11-01.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$56</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,6 +141,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF6EE"/>
       </patternFill>
     </fill>
@@ -152,11 +157,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -239,77 +239,80 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,6 +322,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -328,58 +340,55 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -392,13 +401,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -764,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -915,15 +921,16 @@
               <color rgb="001F2937"/>
               <sz val="10"/>
             </rPr>
-            <t>：引用溯源解题辅导 + 按难度出题 + 学习者记忆闭环</t>
+            <t>：引用溯源解题辅导 + 按难度出题 + 学习者记忆闭环
+团队：核心人物背调沿用 2026-10-29 结果</t>
           </r>
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>3969</v>
+        <v>5899</v>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
@@ -932,7 +939,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>10-28 #9 +1,598 → 10-29 #4 +2,371</t>
+          <t>10-28 #9 +1,598 → 10-29 #4 +2,371 → 10-30 #1 +1,930</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -1220,7 +1227,7 @@
           </r>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="23" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="8" t="n">
@@ -1319,17 +1326,17 @@
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>the-craft-of-selfteaching</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1350,70 +1357,70 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="28" t="n">
         <v>148</v>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t>10-29 #14 +148</t>
         </is>
       </c>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>李笑来（xiaolai）</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>作者</t>
         </is>
       </c>
-      <c r="J8" s="25" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>长春大学会计学专业</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t>原新东方国外部高级教师（2001–2008）；2008 年创立艾德睿智国际教育咨询；2013 年创立比特基金，INBlockchain 硬币资本创始人；著《把时间当作朋友》《财富自由之路》等</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="L8" s="26" t="inlineStr">
         <is>
           <t>北京（GitHub 资料）</t>
         </is>
       </c>
-      <c r="M8" s="25" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t>lixiaolai@gmail.com</t>
         </is>
       </c>
-      <c r="N8" s="30" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O8" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P8" s="25" t="inlineStr">
+      <c r="N8" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O8" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P8" s="26" t="inlineStr">
         <is>
           <t>X
 个人站
 GitHub</t>
         </is>
       </c>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
@@ -1451,12 +1458,12 @@
           </r>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1523,13 +1530,13 @@
       </c>
     </row>
     <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="33" t="n"/>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="33" t="n"/>
+      <c r="A10" s="34" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Donough Liu（GitHub ldm0）</t>
@@ -1630,29 +1637,132 @@
           <t>未查到</t>
         </is>
       </c>
-      <c r="P11" s="34" t="inlineStr">
+      <c r="P11" s="35" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="Q11" s="34" t="inlineStr">
+      <c r="Q11" s="35" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>空间生成式 AI 平台</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>：一个物理感知的 JST 模型生成 3D 场景、角色和动作，驱动 Viggle 视频、PINOC 3D 角色动画和 Viggle Games；自称 4,500 万+用户、a16z 投资</t>
+          </r>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>联合创始人兼 CEO（2022 年起）</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="inlineStr">
+        <is>
+          <t>上海交通大学信息工程本科（2009–2013）；康奈尔大学电子与计算机工程硕士（2013–2015）；多伦多大学 CS 博士候选人（2016–2020，师从 Raquel Urtasun、Sanja Fidler）</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>Autodesk 首席 AI 研究员（2020–2022，3D 生成模型）；Facebook 研究实习（2019–2020）；2022 年创立 Viggle，2024 年获 a16z 领投 1,900 万美元 A 轮</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>多伦多</t>
+        </is>
+      </c>
+      <c r="M12" s="26" t="inlineStr">
+        <is>
+          <t>chuhang1122@gmail.com</t>
+        </is>
+      </c>
+      <c r="N12" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O12" s="37" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P12" s="38" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="Q12" s="26" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>LinkSwift</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1673,86 +1783,86 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="38" t="n">
+      <c r="D13" s="42" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E13" s="43" t="n">
         <v>1616</v>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F13" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="G13" s="41" t="inlineStr">
         <is>
           <t>10-18/29 #11 +1,616</t>
         </is>
       </c>
-      <c r="H12" s="41" t="inlineStr">
+      <c r="H13" s="45" t="inlineStr">
         <is>
           <t>Hmjz100（真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I12" s="37" t="inlineStr">
+      <c r="I13" s="41" t="inlineStr">
         <is>
           <t>作者，GitHub 贡献 326 次，几乎独立维护</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K12" s="37" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K13" s="41" t="inlineStr">
         <is>
           <t>GitHub 简介自称独立开发者；资料中公司/城市为虚构（虚拟学院、虚拟城）</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P12" s="37" t="inlineStr">
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P13" s="41" t="inlineStr">
         <is>
           <t>GitHub
 博客</t>
         </is>
       </c>
-      <c r="Q12" s="37" t="inlineStr">
+      <c r="Q13" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="106" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
+    <row r="14" ht="106" customHeight="1">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>Agent-Reach</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1773,148 +1883,148 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D14" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="43" t="n">
+      <c r="E14" s="47" t="n">
         <v>746</v>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F14" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="G14" s="41" t="inlineStr">
         <is>
           <t>10-13/27 #10 +746</t>
         </is>
       </c>
-      <c r="H13" s="41" t="inlineStr">
+      <c r="H14" s="45" t="inlineStr">
         <is>
           <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I13" s="37" t="inlineStr">
+      <c r="I14" s="41" t="inlineStr">
         <is>
           <t>Solo founder / 主要作者与维护者（华人主导：中文 README、foxmail、Bilibili/小红书渠道、UTC+8 活跃）</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K13" s="37" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K14" s="41" t="inlineStr">
         <is>
           <t>自称 Solo founder（All employees are AI）；主导 Agent-Reach、xfetch 等开源项目；自 2020 年起在 GitHub 活跃</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>未查到（个人页标注 When I Code UTC+8，不足以定城市）</t>
         </is>
       </c>
-      <c r="M13" s="37" t="inlineStr">
+      <c r="M14" s="41" t="inlineStr">
         <is>
           <t>pnt01@foxmail.com</t>
         </is>
       </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P13" s="37" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P14" s="41" t="inlineStr">
         <is>
           <t>X
 GitHub
 discord</t>
         </is>
       </c>
-      <c r="Q13" s="37" t="inlineStr">
+      <c r="Q14" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="39" t="inlineStr">
         <is>
           <t>ziwei-doushu</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>紫微斗数开源排盘引擎（倪海厦《天纪》体系）+ 67.5 万命盘×13 维解读数据集 v4.0；商业站 metisziwei.com</t>
         </is>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D15" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E15" s="43" t="n">
         <v>199</v>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F15" s="44" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="37" t="inlineStr">
+      <c r="G15" s="41" t="inlineStr">
         <is>
           <t>10-25/26 #7 +199</t>
         </is>
       </c>
-      <c r="H14" s="41" t="inlineStr">
+      <c r="H15" s="45" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I14" s="37" t="inlineStr">
+      <c r="I15" s="41" t="inlineStr">
         <is>
           <t>作者 / Metis 创始人，自称一人用 AI 做出商业化 SaaS</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K14" s="37" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K15" s="41" t="inlineStr">
         <is>
           <t>Metis紫微创始人；称专业版订阅超 800、注册超 1 万</t>
         </is>
       </c>
-      <c r="L14" s="37" t="inlineStr">
+      <c r="L15" s="41" t="inlineStr">
         <is>
           <t>重庆（运营主体注册地）</t>
         </is>
       </c>
-      <c r="M14" s="37" t="inlineStr">
+      <c r="M15" s="41" t="inlineStr">
         <is>
           <t>wdy778@outlook.com</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P14" s="37" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P15" s="41" t="inlineStr">
         <is>
           <t>X
 王多鱼AI2.0
@@ -1922,14 +2032,14 @@
 GitHub</t>
         </is>
       </c>
-      <c r="Q14" s="37" t="inlineStr">
+      <c r="Q15" s="41" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Q14"/>
+  <autoFilter ref="A3:Q15"/>
   <mergeCells count="16">
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="E9:E11"/>
@@ -1957,8 +2067,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2086,10 +2199,10 @@
           <t>总星 40,678，「反 AI 味」设计 skill</t>
         </is>
       </c>
-      <c r="E4" s="45" t="n">
+      <c r="E4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="46" t="n">
+      <c r="F4" s="49" t="n">
         <v>8501</v>
       </c>
       <c r="G4" s="18" t="n">
@@ -2139,17 +2252,17 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>总星 92,607，给编程 agent 的设计词汇表</t>
-        </is>
-      </c>
-      <c r="E5" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="46" t="n">
-        <v>5519</v>
+          <t>总星 95,278，给编程 agent 的设计词汇表</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="49" t="n">
+        <v>8389</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>1506</v>
+        <v>2870</v>
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
@@ -2158,7 +2271,7 @@
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
-          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506 → 10-28 #5 +1,449 → 10-29 #7 +1,472</t>
+          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506 → 10-28 #5 +1,449 → 10-29 #7 +1,472 → 10-30 #3 +2,870🚀</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -2177,10 +2290,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="50" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>🚀 cindy</t>
+          <t>🚀 thinkrail</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -2190,22 +2303,22 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>开发工具</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>总星 8,085，心动出品的开源 AI Agent</t>
-        </is>
-      </c>
-      <c r="E6" s="45" t="n">
+          <t>总星 5,988，JetBrains 轻量 Vibe Coding IDE</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="46" t="n">
-        <v>4164</v>
+      <c r="F6" s="49" t="n">
+        <v>4613</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>1465</v>
+        <v>1204</v>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
@@ -2214,17 +2327,17 @@
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀 → 10-28 #6 +1,465 → 10-29 #8 +728</t>
+          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀 → 10-28 #10 +1,204 → 10-29 #1 +1,068 → 10-30 #4 +1,117</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t>心动网络</t>
+          <t>JetBrains 官方</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr">
         <is>
-          <t>XD；官方项目，不计独立</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
@@ -2236,7 +2349,7 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>🚀 thinkrail</t>
+          <t>🚀 cindy</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -2246,22 +2359,22 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>开发工具</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>总星 5,017，JetBrains 轻量 Vibe Coding IDE</t>
-        </is>
-      </c>
-      <c r="E7" s="45" t="n">
+          <t>总星 8,085，心动出品的开源 AI Agent</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="46" t="n">
-        <v>3496</v>
+      <c r="F7" s="49" t="n">
+        <v>4164</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1204</v>
+        <v>1465</v>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
@@ -2270,17 +2383,17 @@
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀 → 10-28 #10 +1,204 → 10-29 #1 +1,068</t>
+          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀 → 10-28 #6 +1,465 → 10-29 #8 +728</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>JetBrains 官方</t>
+          <t>心动网络</t>
         </is>
       </c>
       <c r="K7" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>XD；官方项目，不计独立</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -2307,17 +2420,17 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>总星 7,079，越狱提示词合集</t>
-        </is>
-      </c>
-      <c r="E8" s="47" t="n">
+          <t>总星 8,989，越狱提示词合集</t>
+        </is>
+      </c>
+      <c r="E8" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="F8" s="46" t="n">
-        <v>2379</v>
+      <c r="F8" s="49" t="n">
+        <v>3973</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>1477</v>
+        <v>1594</v>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
@@ -2326,12 +2439,12 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>10-28 #11 +902 → 10-29 #10 +1,477🚀</t>
+          <t>10-28 #11 +902 → 10-29 #10 +1,477🚀 → 10-30 #10 +1,594</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t>提示词合集，按规则不计</t>
+          <t>提示词合集，不计</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
@@ -2346,56 +2459,56 @@
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>ECC</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>🚀 superpowers</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>总星 290,865，Agent harness 性能优化系统</t>
-        </is>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>2061</v>
-      </c>
-      <c r="G9" s="48" t="n">
-        <v>1165</v>
-      </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>总星 308,526，agentic skills 框架 + 开发方法论</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="49" t="n">
+        <v>2746</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
-        <is>
-          <t>10-27 #5 +896 → 10-28 #8 +1,165</t>
-        </is>
-      </c>
-      <c r="J9" s="29" t="inlineStr">
-        <is>
-          <t>Affaan Mustafa，非华人</t>
-        </is>
-      </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>10-28 #4 +617 → 10-29 #3 +1,095🚀 → 10-30 #2 +1,034</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>非华人</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2419,14 +2532,14 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>总星 3,235，本地优先的持久 AI 队友桌面工作区</t>
+          <t>总星 3,862，本地优先的持久 AI 队友桌面工作区</t>
         </is>
       </c>
       <c r="E10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="46" t="n">
-        <v>2007</v>
+      <c r="F10" s="49" t="n">
+        <v>2716</v>
       </c>
       <c r="G10" s="18" t="n">
         <v>1054</v>
@@ -2438,7 +2551,7 @@
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
-          <t>10-27 #9 +176 → 10-28 #3 +777🚀 → 10-29 #9 +1,054</t>
+          <t>10-27 #9 +176 → 10-28 #3 +777🚀 → 10-29 #9 +1,054 → 10-30 #6 +709</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -2458,56 +2571,56 @@
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>🚀 superpowers</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ECC</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>总星 307,428，agentic skills 框架 + 开发方法论</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="46" t="n">
-        <v>1712</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>1095</v>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>总星 290,865，Agent harness 性能优化系统</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>2061</v>
+      </c>
+      <c r="G11" s="51" t="n">
+        <v>1165</v>
+      </c>
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>10-28 #4 +617 → 10-29 #3 +1,095🚀</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>非华人</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>10-27 #5 +896 → 10-28 #8 +1,165</t>
+        </is>
+      </c>
+      <c r="J11" s="30" t="inlineStr">
+        <is>
+          <t>Affaan Mustafa，非华人</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
+      <c r="L11" s="32" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2534,10 +2647,10 @@
           <t>总星 12,395，迷你双足小鸭机器人 🦆</t>
         </is>
       </c>
-      <c r="E12" s="47" t="n">
+      <c r="E12" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="46" t="n">
+      <c r="F12" s="49" t="n">
         <v>1490</v>
       </c>
       <c r="G12" s="18" t="n">
@@ -2570,58 +2683,58 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>TheySaid 4.0</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Empacer</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>317 票，在你搭产品的地方直接预演用户反应</t>
-        </is>
-      </c>
-      <c r="E13" s="49" t="n">
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>小商家的语音优先助手，说一句话出回复、帖子、发票</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="50" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="50" t="inlineStr">
+      <c r="G13" s="36" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="51" t="n">
-        <v>317</v>
-      </c>
-      <c r="I13" s="25" t="inlineStr">
-        <is>
-          <t>10-27 #1</t>
-        </is>
-      </c>
-      <c r="J13" s="29" t="inlineStr">
-        <is>
-          <t>快速查未发现华人主导</t>
-        </is>
-      </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="H13" s="53" t="n">
+        <v>379</v>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>10-29 #1</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L13" s="31" t="inlineStr">
+      <c r="L13" s="32" t="inlineStr">
         <is>
           <t>未查到</t>
         </is>
@@ -2630,223 +2743,223 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>TheySaid 4.0</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>317 票，在你搭产品的地方直接预演用户反应</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="54" t="n">
+        <v>317</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>10-27 #1</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>快速查未发现华人主导</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Scape</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>自动排优先级、备好回复草稿的智能邮箱</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="53" t="n">
+        <v>285</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>10-29 #2</t>
+        </is>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Overmind</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>272 票，开源的持续学习平台</t>
         </is>
       </c>
-      <c r="E14" s="52" t="n">
+      <c r="E16" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="53" t="n">
+      <c r="H16" s="54" t="n">
         <v>272</v>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>10-27 #2</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>快速查未发现华人主导</t>
         </is>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Strawberry 1.0</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>内置 AI Companions 的浏览器，替团队干调研 / 跟进 / 行政杂活</t>
-        </is>
-      </c>
-      <c r="E15" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="50" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>VoiceStudio</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>总星 89,187，本地开源 ElevenLabs 替代，语音克隆 / 配音 / 多语种</t>
+        </is>
+      </c>
+      <c r="E17" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="47" t="n">
+        <v>3889</v>
+      </c>
+      <c r="G17" s="58" t="n">
+        <v>2297</v>
+      </c>
+      <c r="H17" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="51" t="n">
-        <v>265</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>10-26 #1</t>
-        </is>
-      </c>
-      <c r="J15" s="29" t="inlineStr">
-        <is>
-          <t>未发现华人主导</t>
-        </is>
-      </c>
-      <c r="K15" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Dedica</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>测你的网站能不能被 AI agent 用（文案点名 Muse、Instinct、GrokBot），125 项免费检查</t>
-        </is>
-      </c>
-      <c r="E16" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="53" t="n">
-        <v>261</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>10-28 #1</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>VoiceStudio</t>
-        </is>
-      </c>
-      <c r="B17" s="36" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="D17" s="37" t="inlineStr">
-        <is>
-          <t>总星 89,187，本地开源 ElevenLabs 替代，语音克隆 / 配音 / 多语种</t>
-        </is>
-      </c>
-      <c r="E17" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="39" t="n">
-        <v>3889</v>
-      </c>
-      <c r="G17" s="55" t="n">
-        <v>2297</v>
-      </c>
-      <c r="H17" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="37" t="inlineStr">
+      <c r="I17" s="41" t="inlineStr">
         <is>
           <t>10-18/26 #3 +1,592 → 10-27 #11 +2,297</t>
         </is>
       </c>
-      <c r="J17" s="41" t="inlineStr">
+      <c r="J17" s="45" t="inlineStr">
         <is>
           <t>Deb Palash，未核实为华人</t>
         </is>
       </c>
-      <c r="K17" s="37" t="inlineStr">
+      <c r="K17" s="41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2899,92 +3012,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="56" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-26 – 11-01）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="57" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 8 个 · 核心人物 11 位</t>
+      <c r="B2" s="60" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 9 个 · 核心人物 12 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="58" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-29（第 4/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="63" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-30（第 5/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 Nutlope/hallmark；已收录全球项目 14 个、华人项目 8 个，今日新增华人项目：hmjz100/LinkSwift、xiaolai/the-craft-of-selfteaching。</t>
+      <c r="B6" s="63" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 Nutlope/hallmark；已收录全球项目 14 个、华人项目 9 个，今日新增华人项目：Viggle AI（JST-2）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="63" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="64" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="68" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-11-01/</t>
         </is>
@@ -3005,7 +3118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3077,34 +3190,34 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>https://bingxi.life/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>HKUDS/DeepTutor</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Bingxi Zhao（中文名未查到）</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E5" s="66" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>https://github.com/pancacake</t>
         </is>
@@ -3131,34 +3244,34 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2604.26962</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>HKUDS/DeepTutor</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E7" s="66" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/chaoh</t>
         </is>
@@ -3185,34 +3298,34 @@
           <t>GitHub 组织</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>https://github.com/HKUDS</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>HKUDS/DeepTutor</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Huang Chao（黄超）</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E9" s="66" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>https://datascience.hku.hk/people/chao-huang/</t>
         </is>
@@ -3239,34 +3352,34 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2604.26962</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E11" s="66" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>https://github.com/Yijia-Xiao</t>
         </is>
@@ -3293,34 +3406,34 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>https://yijia-xiao.com/</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E13" s="66" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>https://github.com/TauricResearch/TradingAgents</t>
         </is>
@@ -3347,34 +3460,34 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>https://tauric.ai/contact/</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>TauricResearch/TradingAgents</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>肖一嘉（Yijia Xiao）</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E15" s="66" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>https://tauric.ai/research/tradingagents</t>
         </is>
@@ -3401,34 +3514,34 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>https://x.com/AlchainHust</t>
         </is>
       </c>
     </row>
     <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="E17" s="66" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/</t>
         </is>
@@ -3455,34 +3568,34 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>https://github.com/alchaincyf</t>
         </is>
       </c>
     </row>
     <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E19" s="66" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/insights/wechat-2247485096-1/</t>
         </is>
@@ -3509,34 +3622,34 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/consulting/</t>
         </is>
       </c>
     </row>
     <row r="21" ht="50" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>alchaincyf/huashu-design</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>花叔（公开常用名；亦作花生 / Alchain；真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>来源5</t>
         </is>
       </c>
-      <c r="E21" s="66" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>https://github.com/alchaincyf/huashu-design</t>
         </is>
@@ -3563,34 +3676,34 @@
           <t>来源6</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>https://m.okjike.com/users/27BF807A-FA4D-4B01-AAFD-05FAAA674335</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>xiaolai/the-craft-of-selfteaching</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>李笑来（xiaolai）</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E23" s="66" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>https://x.com/xiaolai</t>
         </is>
@@ -3617,34 +3730,34 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr">
         <is>
           <t>http://lixiaolai.com</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>xiaolai/the-craft-of-selfteaching</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>李笑来（xiaolai）</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E25" s="66" t="inlineStr">
+      <c r="E25" s="38" t="inlineStr">
         <is>
           <t>https://github.com/xiaolai</t>
         </is>
@@ -3671,34 +3784,34 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>https://zh.wikipedia.org/wiki/%E6%9D%8E%E7%AC%91%E6%9D%A5</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E27" s="66" t="inlineStr">
+      <c r="E27" s="38" t="inlineStr">
         <is>
           <t>https://wenjiai.cn/products/lanyue-ai</t>
         </is>
@@ -3725,34 +3838,34 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>https://vc.pedaily.cn/company/865282.html</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E29" s="66" t="inlineStr">
+      <c r="E29" s="38" t="inlineStr">
         <is>
           <t>https://browser.lexmount.cn/about</t>
         </is>
@@ -3779,34 +3892,34 @@
           <t>来源4</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>https://browser.lexmount.cn/privacy</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>来源5</t>
         </is>
       </c>
-      <c r="E31" s="66" t="inlineStr">
+      <c r="E31" s="38" t="inlineStr">
         <is>
           <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
         </is>
@@ -3833,34 +3946,34 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t>https://github.com/ldm0</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>v2ex</t>
         </is>
       </c>
-      <c r="E33" s="66" t="inlineStr">
+      <c r="E33" s="38" t="inlineStr">
         <is>
           <t>https://www.v2ex.com/t/1236833</t>
         </is>
@@ -3887,34 +4000,34 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>https://github.com/lexmount/moli</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E35" s="66" t="inlineStr">
+      <c r="E35" s="38" t="inlineStr">
         <is>
           <t>https://www.producthunt.com/products/lexmount-browser</t>
         </is>
@@ -3941,34 +4054,34 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E36" s="34" t="inlineStr">
+      <c r="E36" s="35" t="inlineStr">
         <is>
           <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Nico Hu</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E37" s="66" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>https://www.producthunt.com/products/lexmount-browser</t>
         </is>
@@ -3977,216 +4090,216 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>hmjz100/LinkSwift</t>
+          <t>Viggle AI（JST-2）</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Hmjz100（真实姓名未查到）</t>
+          <t>Hang Chu（中文名未查到）</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hang-chu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E38" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/hmjz100</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="29" t="inlineStr">
-        <is>
-          <t>hmjz100/LinkSwift</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="inlineStr">
-        <is>
-          <t>Hmjz100（真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="inlineStr">
-        <is>
-          <t>博客</t>
-        </is>
-      </c>
-      <c r="E39" s="66" t="inlineStr">
-        <is>
-          <t>https://hmjz100blog.rf.gd</t>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E39" s="38" t="inlineStr">
+        <is>
+          <t>http://chuhang.github.io</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>http://chuhang.github.io/files/resume.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E41" s="38" t="inlineStr">
+        <is>
+          <t>https://thelogic.co/briefing/torontos-viggle-ai-raises-us19m-series-a-led-by-a16z-for-generative-animation-tools/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>https://theorg.com/org/viggle/org-chart/hang-chu</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
           <t>hmjz100/LinkSwift</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>Hmjz100（真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E43" s="38" t="inlineStr">
+        <is>
+          <t>https://github.com/hmjz100</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>hmjz100/LinkSwift</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Hmjz100（真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>博客</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="inlineStr">
+        <is>
+          <t>https://hmjz100blog.rf.gd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="30" t="inlineStr">
+        <is>
+          <t>hmjz100/LinkSwift</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>Hmjz100（真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E40" s="34" t="inlineStr">
+      <c r="E45" s="38" t="inlineStr">
         <is>
           <t>https://github.com/hmjz100/LinkSwift</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="64" customHeight="1">
-      <c r="A41" s="29" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E41" s="66" t="inlineStr">
-        <is>
-          <t>https://x.com/Neo_Reidlab</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="64" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E42" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="64" customHeight="1">
-      <c r="A43" s="29" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>discord</t>
-        </is>
-      </c>
-      <c r="E43" s="66" t="inlineStr">
-        <is>
-          <t>https://discord.gg/NSZz22R39</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E44" s="34" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="64" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D45" s="25" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E45" s="66" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
         </is>
       </c>
     </row>
@@ -4203,157 +4316,292 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>https://x.com/Neo_Reidlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E47" s="38" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>discord</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>https://discord.gg/NSZz22R39</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E49" s="38" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E46" s="34" t="inlineStr">
+      <c r="E51" s="38" t="inlineStr">
         <is>
           <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="29" t="inlineStr">
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D47" s="25" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E47" s="66" t="inlineStr">
+      <c r="E52" s="35" t="inlineStr">
         <is>
           <t>https://x.com/wdy188</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C53" s="25" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E48" s="34" t="inlineStr">
+      <c r="E53" s="38" t="inlineStr">
         <is>
           <t>https://github.com/Renhuai123</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B49" s="25" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C49" s="24" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D49" s="25" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>来源2</t>
         </is>
       </c>
-      <c r="E49" s="66" t="inlineStr">
+      <c r="E54" s="35" t="inlineStr">
         <is>
           <t>https://github.com/Renhuai123/ziwei-doushu</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C55" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>来源3</t>
         </is>
       </c>
-      <c r="E50" s="34" t="inlineStr">
+      <c r="E55" s="38" t="inlineStr">
         <is>
           <t>https://metisziwei.com/privacy</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="29" t="inlineStr">
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B51" s="25" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D51" s="25" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E51" s="66" t="inlineStr">
+      <c r="E56" s="35" t="inlineStr">
         <is>
           <t>https://zamantika.com/profile/wdy188</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E51"/>
+  <autoFilter ref="A3:E56"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -4407,6 +4655,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>

--- a/2026-11-01/weekly-2026-11-01.xlsx
+++ b/2026-11-01/weekly-2026-11-01.xlsx
@@ -13,15 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="链接" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'华人项目'!$A$3:$Q$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'华人项目'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'华人项目'!$A$1:$Q$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全球项目'!$A$3:$L$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全球项目'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'全球项目'!$A$1:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'链接'!$A$3:$E$67</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'链接'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'链接'!$A$1:$E$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -315,22 +315,34 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -367,22 +379,19 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -770,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -930,7 +939,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>5899</v>
+        <v>8181</v>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
@@ -939,7 +948,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>10-28 #9 +1,598 → 10-29 #4 +2,371 → 10-30 #1 +1,930</t>
+          <t>10-28 #9 +1,598 → 10-29 #4 +2,371 → 10-30 #1 +1,930 → 10-31 #10 +2,282</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -1426,18 +1435,260 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1">
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>SpeakON Agent</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>iPhone MagSafe 语音按钮 + AI，说话即出文字并由 agent 起草邮件、约会议；Notta 旗下品牌</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>253</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>10-30 #3</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>张岩（Ryan Zhang）</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>SpeakON 创始人兼 CEO；Notta 创始人</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>计算机工程本科，2006 年毕业（院校未查到）</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>网络广告公司；优酷、百度、滴滴、思必驰；摩拜单车联合创始人；2018 年出海翻译机创业；2020 年创立 Notta（用户超 1,000 万）；2026 年 4 月推出 SpeakON</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>未查到（公司总部新加坡）</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Teable Mobile</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>基于 Postgres 的开源 AI 数据库 / Database Agent，本次发布手机版</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="n">
+        <v>103</v>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>10-30 #8</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>陈加贝（Jiabei Chen）</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>创始人兼 CEO；teableio/teable 最大贡献者（GitHub tea-artist）</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="inlineStr">
+        <is>
+          <t>湖南科技大学计算机科学本科（2012–2016）</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <b val="1"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>阿里巴巴</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="微软雅黑"/>
+              <color rgb="001F2937"/>
+              <sz val="10"/>
+            </rPr>
+            <t>实习；Insta360（2015）；字节跳动（2017，飞书多维表格首位工程师）；vika 维格表联合创始人兼 CTO（2019–2022）；2022 年底创立 Teable</t>
+          </r>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>新加坡（LinkedIn 现居）</t>
+        </is>
+      </c>
+      <c r="M10" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N10" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O10" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P10" s="26" t="inlineStr">
+        <is>
+          <t>X
+GitHub</t>
+        </is>
+      </c>
+      <c r="Q10" s="26" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="30" t="inlineStr">
+        <is>
+          <t>Gary Guangyu Li</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>COO</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M11" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N11" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O11" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="P11" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q11" s="40" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1458,208 +1709,208 @@
           </r>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>樊俊超</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>深圳市揽岳智能科技有限公司法定代表人、董事长兼经理</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>未查到（公开报道多写柔宇联合创始人为清华/斯坦福校友群体，未单独证实其学历）</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>柔宇科技联合创始人之一、曾任副总裁（与刘自鸿、魏鹏等）；2025 转向 AI 云端浏览器基础设施创业，创立揽岳智能 / Lexmount</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>深圳（公司注册地）；北京亦有运营主体</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="34" t="n"/>
-      <c r="B10" s="34" t="n"/>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="34" t="n"/>
-      <c r="G10" s="34" t="n"/>
-      <c r="H10" s="10" t="inlineStr">
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="41" t="n"/>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="41" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="G13" s="41" t="n"/>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Moli 核心开发者 / PH maker；lexmount/moli 主要贡献者</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>北京开发者；在创业公司做浏览器相关，主导开源 Moli；V2EX 发帖介绍项目</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>北京（GitHub Location: Beijing China）</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>GitHub
 v2ex</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="13" t="n"/>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="10" t="inlineStr">
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Nico Hu</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>PH maker（自称 one of the makers of Moli by Lexmount）</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>未查到可靠公开履历（同名 LinkedIn 多为生物医药，未核实为同一人）</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M11" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P11" s="35" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P14" s="42" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="Q11" s="35" t="inlineStr">
+      <c r="Q14" s="42" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Viggle AI（JST-2）</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1680,89 +1931,89 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G15" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>Hang Chu（中文名未查到）</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>联合创始人兼 CEO（2022 年起）</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr">
+      <c r="J15" s="26" t="inlineStr">
         <is>
           <t>上海交通大学信息工程本科（2009–2013）；康奈尔大学电子与计算机工程硕士（2013–2015）；多伦多大学 CS 博士候选人（2016–2020，师从 Raquel Urtasun、Sanja Fidler）</t>
         </is>
       </c>
-      <c r="K12" s="26" t="inlineStr">
+      <c r="K15" s="26" t="inlineStr">
         <is>
           <t>Autodesk 首席 AI 研究员（2020–2022，3D 生成模型）；Facebook 研究实习（2019–2020）；2022 年创立 Viggle，2024 年获 a16z 领投 1,900 万美元 A 轮</t>
         </is>
       </c>
-      <c r="L12" s="26" t="inlineStr">
+      <c r="L15" s="26" t="inlineStr">
         <is>
           <t>多伦多</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr">
+      <c r="M15" s="26" t="inlineStr">
         <is>
           <t>chuhang1122@gmail.com</t>
         </is>
       </c>
-      <c r="N12" s="31" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O12" s="37" t="inlineStr">
+      <c r="N15" s="31" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O15" s="39" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="P12" s="38" t="inlineStr">
+      <c r="P15" s="40" t="inlineStr">
         <is>
           <t>个人站</t>
         </is>
       </c>
-      <c r="Q12" s="26" t="inlineStr">
+      <c r="Q15" s="26" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1">
-      <c r="A13" s="39" t="inlineStr">
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>LinkSwift</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="C13" s="41" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1783,86 +2034,173 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D16" s="46" t="n">
         <v>11</v>
       </c>
-      <c r="E13" s="43" t="n">
+      <c r="E16" s="47" t="n">
         <v>1616</v>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F16" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="41" t="inlineStr">
+      <c r="G16" s="45" t="inlineStr">
         <is>
           <t>10-18/29 #11 +1,616</t>
         </is>
       </c>
-      <c r="H13" s="45" t="inlineStr">
+      <c r="H16" s="49" t="inlineStr">
         <is>
           <t>Hmjz100（真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I13" s="41" t="inlineStr">
+      <c r="I16" s="45" t="inlineStr">
         <is>
           <t>作者，GitHub 贡献 326 次，几乎独立维护</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K13" s="41" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K16" s="45" t="inlineStr">
         <is>
           <t>GitHub 简介自称独立开发者；资料中公司/城市为虚构（虚拟学院、虚拟城）</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P13" s="41" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P16" s="45" t="inlineStr">
         <is>
           <t>GitHub
 博客</t>
         </is>
       </c>
-      <c r="Q13" s="41" t="inlineStr">
+      <c r="Q16" s="45" t="inlineStr">
         <is>
           <t>来源1、来源2</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="106" customHeight="1">
-      <c r="A14" s="39" t="inlineStr">
+    <row r="17" ht="92" customHeight="1">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>紫微斗数开源排盘引擎（倪海厦《天纪》体系）+ 67.5 万命盘×13 维解读数据集 v4.0；商业站 metisziwei.com
+团队：核心人物背调沿用 2026-10-24 结果</t>
+        </is>
+      </c>
+      <c r="D17" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="51" t="n">
+        <v>1325</v>
+      </c>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="45" t="inlineStr">
+        <is>
+          <t>10-25/26 #7 +199 → 10-31 #5 +1,126</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="I17" s="45" t="inlineStr">
+        <is>
+          <t>作者 / Metis 创始人，自称一人用 AI 做出商业化 SaaS</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K17" s="45" t="inlineStr">
+        <is>
+          <t>Metis紫微创始人；称专业版订阅超 800、注册超 1 万</t>
+        </is>
+      </c>
+      <c r="L17" s="45" t="inlineStr">
+        <is>
+          <t>重庆（运营主体注册地）</t>
+        </is>
+      </c>
+      <c r="M17" s="45" t="inlineStr">
+        <is>
+          <t>wdy778@outlook.com</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P17" s="45" t="inlineStr">
+        <is>
+          <t>X
+王多鱼AI2.0
+王多鱼AI
+GitHub</t>
+        </is>
+      </c>
+      <c r="Q17" s="45" t="inlineStr">
+        <is>
+          <t>来源1、来源2、来源3、来源4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="106" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>Agent-Reach</t>
         </is>
       </c>
-      <c r="B14" s="40" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>智能体工具</t>
         </is>
       </c>
-      <c r="C14" s="41" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1883,180 +2221,101 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="46" t="n">
+      <c r="D18" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E18" s="47" t="n">
         <v>746</v>
       </c>
-      <c r="F14" s="48" t="inlineStr">
+      <c r="F18" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="41" t="inlineStr">
+      <c r="G18" s="45" t="inlineStr">
         <is>
           <t>10-13/27 #10 +746</t>
         </is>
       </c>
-      <c r="H14" s="45" t="inlineStr">
+      <c r="H18" s="49" t="inlineStr">
         <is>
           <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
         </is>
       </c>
-      <c r="I14" s="41" t="inlineStr">
+      <c r="I18" s="45" t="inlineStr">
         <is>
           <t>Solo founder / 主要作者与维护者（华人主导：中文 README、foxmail、Bilibili/小红书渠道、UTC+8 活跃）</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K14" s="41" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="K18" s="45" t="inlineStr">
         <is>
           <t>自称 Solo founder（All employees are AI）；主导 Agent-Reach、xfetch 等开源项目；自 2020 年起在 GitHub 活跃</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>未查到（个人页标注 When I Code UTC+8，不足以定城市）</t>
         </is>
       </c>
-      <c r="M14" s="41" t="inlineStr">
+      <c r="M18" s="45" t="inlineStr">
         <is>
           <t>pnt01@foxmail.com</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P14" s="41" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+      <c r="P18" s="45" t="inlineStr">
         <is>
           <t>X
 GitHub
 discord</t>
         </is>
       </c>
-      <c r="Q14" s="41" t="inlineStr">
+      <c r="Q18" s="45" t="inlineStr">
         <is>
           <t>来源1、来源2、来源3、来源4、来源5</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>ziwei-doushu</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C15" s="41" t="inlineStr">
-        <is>
-          <t>紫微斗数开源排盘引擎（倪海厦《天纪》体系）+ 67.5 万命盘×13 维解读数据集 v4.0；商业站 metisziwei.com</t>
-        </is>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" s="43" t="n">
-        <v>199</v>
-      </c>
-      <c r="F15" s="44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="41" t="inlineStr">
-        <is>
-          <t>10-25/26 #7 +199</t>
-        </is>
-      </c>
-      <c r="H15" s="45" t="inlineStr">
-        <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="I15" s="41" t="inlineStr">
-        <is>
-          <t>作者 / Metis 创始人，自称一人用 AI 做出商业化 SaaS</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="K15" s="41" t="inlineStr">
-        <is>
-          <t>Metis紫微创始人；称专业版订阅超 800、注册超 1 万</t>
-        </is>
-      </c>
-      <c r="L15" s="41" t="inlineStr">
-        <is>
-          <t>重庆（运营主体注册地）</t>
-        </is>
-      </c>
-      <c r="M15" s="41" t="inlineStr">
-        <is>
-          <t>wdy778@outlook.com</t>
-        </is>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-      <c r="P15" s="41" t="inlineStr">
-        <is>
-          <t>X
-王多鱼AI2.0
-王多鱼AI
-GitHub</t>
-        </is>
-      </c>
-      <c r="Q15" s="41" t="inlineStr">
-        <is>
-          <t>来源1、来源2、来源3、来源4</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:Q15"/>
-  <mergeCells count="16">
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="G9:G11"/>
+  <autoFilter ref="A3:Q18"/>
+  <mergeCells count="23">
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -2064,14 +2323,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId18"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2178,10 +2442,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="50" customHeight="1">
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>🚀 hallmark</t>
+          <t>🚀 impeccable</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -2196,17 +2460,17 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>总星 40,678，「反 AI 味」设计 skill</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="49" t="n">
-        <v>8501</v>
+          <t>总星 97,036，给编程 agent 的设计词汇表</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="53" t="n">
+        <v>10689</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>2830</v>
+        <v>2870</v>
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
@@ -2215,7 +2479,7 @@
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
-          <t>10-26 #2 +1,317🚀 → 10-27 #1 +2,244🚀 → 10-28 #2 +2,830 → 10-29 #6 +2,110</t>
+          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506 → 10-28 #5 +1,449 → 10-29 #7 +1,472 → 10-30 #3 +2,870🚀 → 10-31 #3 +2,300</t>
         </is>
       </c>
       <c r="J4" s="20" t="inlineStr">
@@ -2237,7 +2501,7 @@
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>🚀 impeccable</t>
+          <t>🚀 hallmark</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -2252,17 +2516,17 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>总星 95,278，给编程 agent 的设计词汇表</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="49" t="n">
-        <v>8389</v>
+          <t>总星 40,678，「反 AI 味」设计 skill</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="53" t="n">
+        <v>8501</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>2870</v>
+        <v>2830</v>
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
@@ -2271,7 +2535,7 @@
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
-          <t>10-26 #4 +1,092🚀 → 10-27 #6 +1,506 → 10-28 #5 +1,449 → 10-29 #7 +1,472 → 10-30 #3 +2,870🚀</t>
+          <t>10-26 #2 +1,317🚀 → 10-27 #1 +2,244🚀 → 10-28 #2 +2,830 → 10-29 #6 +2,110</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -2293,88 +2557,88 @@
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
+          <t>🚀 jailbreaks</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>总星 10,974，越狱提示词合集</t>
+        </is>
+      </c>
+      <c r="E6" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="53" t="n">
+        <v>6028</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>2055</v>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>10-28 #11 +902 → 10-29 #10 +1,477🚀 → 10-30 #10 +1,594 → 10-31 #13 +2,055</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>提示词合集，不计</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>🚀 thinkrail</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>开发工具</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>总星 5,988，JetBrains 轻量 Vibe Coding IDE</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="49" t="n">
-        <v>4613</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>1204</v>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀 → 10-28 #10 +1,204 → 10-29 #1 +1,068 → 10-30 #4 +1,117</t>
-        </is>
-      </c>
-      <c r="J6" s="20" t="inlineStr">
-        <is>
-          <t>JetBrains 官方</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>🚀 cindy</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>总星 8,085，心动出品的开源 AI Agent</t>
+          <t>总星 6,569，JetBrains 轻量 Vibe Coding IDE</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="49" t="n">
-        <v>4164</v>
+      <c r="F7" s="53" t="n">
+        <v>5335</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1465</v>
+        <v>1204</v>
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
@@ -2383,17 +2647,17 @@
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀 → 10-28 #6 +1,465 → 10-29 #8 +728</t>
+          <t>10-26 #8 +51 → 10-27 #3 +1,173🚀 → 10-28 #10 +1,204 → 10-29 #1 +1,068 → 10-30 #4 +1,117 → 10-31 #12 +722</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>心动网络</t>
+          <t>JetBrains 官方</t>
         </is>
       </c>
       <c r="K7" s="16" t="inlineStr">
         <is>
-          <t>XD；官方项目，不计独立</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L7" s="22" t="inlineStr">
@@ -2405,7 +2669,7 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>🚀 jailbreaks</t>
+          <t>🚀 cindy</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -2420,17 +2684,17 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>总星 8,989，越狱提示词合集</t>
-        </is>
-      </c>
-      <c r="E8" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="49" t="n">
-        <v>3973</v>
+          <t>总星 8,085，心动出品的开源 AI Agent</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="53" t="n">
+        <v>4164</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>1594</v>
+        <v>1465</v>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
@@ -2439,17 +2703,17 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>10-28 #11 +902 → 10-29 #10 +1,477🚀 → 10-30 #10 +1,594</t>
+          <t>10-26 #1 +675 → 10-27 #4 +1,296🚀 → 10-28 #6 +1,465 → 10-29 #8 +728</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t>提示词合集，不计</t>
+          <t>心动网络</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>XD；官方项目，不计独立</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
@@ -2458,7 +2722,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>🚀 superpowers</t>
@@ -2476,17 +2740,17 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>总星 308,526，agentic skills 框架 + 开发方法论</t>
+          <t>总星 309,416，agentic skills 框架 + 开发方法论</t>
         </is>
       </c>
       <c r="E9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="49" t="n">
-        <v>2746</v>
+      <c r="F9" s="53" t="n">
+        <v>4005</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>1095</v>
+        <v>1259</v>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
@@ -2495,7 +2759,7 @@
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
-          <t>10-28 #4 +617 → 10-29 #3 +1,095🚀 → 10-30 #2 +1,034</t>
+          <t>10-28 #4 +617 → 10-29 #3 +1,095🚀 → 10-30 #2 +1,034 → 10-31 #14 +1,259</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -2538,7 +2802,7 @@
       <c r="E10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="53" t="n">
         <v>2716</v>
       </c>
       <c r="G10" s="18" t="n">
@@ -2573,112 +2837,112 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
+          <t>OpenMausBot</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>总星 8,618，自称「开源版 Grok Bot 替代」，给 bot 配虚拟机</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>2094</v>
+      </c>
+      <c r="G11" s="56" t="n">
+        <v>1199</v>
+      </c>
+      <c r="H11" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>10-30 #5 +1,199 → 10-31 #2 +895</t>
+        </is>
+      </c>
+      <c r="J11" s="30" t="inlineStr">
+        <is>
+          <t>Milind Soni，未见华人主导</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>未查到</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>ECC</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>总星 290,865，Agent harness 性能优化系统</t>
         </is>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E12" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F12" s="8" t="n">
         <v>2061</v>
       </c>
-      <c r="G11" s="51" t="n">
+      <c r="G12" s="57" t="n">
         <v>1165</v>
       </c>
-      <c r="H11" s="29" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>10-27 #5 +896 → 10-28 #8 +1,165</t>
         </is>
       </c>
-      <c r="J11" s="30" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Affaan Mustafa，非华人</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L11" s="32" t="inlineStr">
-        <is>
-          <t>未查到</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>🚀 microduck</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>总星 12,395，迷你双足小鸭机器人 🦆</t>
-        </is>
-      </c>
-      <c r="E12" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="49" t="n">
-        <v>1490</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>843</v>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>10-26 #5 +647🚀 → 10-27 #8 +843</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>Pollen Robotics</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>法国</t>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>未查到</t>
         </is>
       </c>
     </row>
@@ -2703,20 +2967,20 @@
           <t>小商家的语音优先助手，说一句话出回复、帖子、发票</t>
         </is>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="36" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="53" t="n">
+      <c r="H13" s="38" t="n">
         <v>379</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
@@ -2761,20 +3025,20 @@
           <t>317 票，在你搭产品的地方直接预演用户反应</t>
         </is>
       </c>
-      <c r="E14" s="52" t="n">
+      <c r="E14" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="33" t="inlineStr">
+      <c r="F14" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="33" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="54" t="n">
+      <c r="H14" s="35" t="n">
         <v>317</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -2819,20 +3083,20 @@
           <t>自动排优先级、备好回复草稿的智能邮箱</t>
         </is>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="36" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="36" t="inlineStr">
+      <c r="G15" s="37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="53" t="n">
+      <c r="H15" s="38" t="n">
         <v>285</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
@@ -2877,20 +3141,20 @@
           <t>272 票，开源的持续学习平台</t>
         </is>
       </c>
-      <c r="E16" s="56" t="n">
+      <c r="E16" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="33" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="33" t="inlineStr">
+      <c r="G16" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="54" t="n">
+      <c r="H16" s="35" t="n">
         <v>272</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -2915,51 +3179,51 @@
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>VoiceStudio</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>语音</t>
         </is>
       </c>
-      <c r="D17" s="41" t="inlineStr">
+      <c r="D17" s="45" t="inlineStr">
         <is>
           <t>总星 89,187，本地开源 ElevenLabs 替代，语音克隆 / 配音 / 多语种</t>
         </is>
       </c>
-      <c r="E17" s="57" t="n">
+      <c r="E17" s="60" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="47" t="n">
+      <c r="F17" s="51" t="n">
         <v>3889</v>
       </c>
-      <c r="G17" s="58" t="n">
+      <c r="G17" s="61" t="n">
         <v>2297</v>
       </c>
-      <c r="H17" s="48" t="inlineStr">
+      <c r="H17" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="41" t="inlineStr">
+      <c r="I17" s="45" t="inlineStr">
         <is>
           <t>10-18/26 #3 +1,592 → 10-27 #11 +2,297</t>
         </is>
       </c>
-      <c r="J17" s="45" t="inlineStr">
+      <c r="J17" s="49" t="inlineStr">
         <is>
           <t>Deb Palash，未核实为华人</t>
         </is>
       </c>
-      <c r="K17" s="41" t="inlineStr">
+      <c r="K17" s="45" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3012,92 +3276,92 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>每周开源 / 产品 Sourcing 周报（2026-10-26 – 11-01）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="60" t="inlineStr">
-        <is>
-          <t>全球项目 14 个 · 华人项目 9 个 · 核心人物 12 位</t>
+      <c r="B2" s="63" t="inlineStr">
+        <is>
+          <t>全球项目 14 个 · 华人项目 11 个 · 核心人物 15 位</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="64" t="inlineStr">
         <is>
           <t>本周总览</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B5" s="63" t="inlineStr">
-        <is>
-          <t>本周进行中 · 已更新至 10-30（第 5/7 天），每天日报后自动刷新。</t>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>本周进行中 · 已更新至 10-31（第 6/7 天），每天日报后自动刷新。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="65" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B6" s="63" t="inlineStr">
-        <is>
-          <t>本周 GitHub 累计星增第一是 Nutlope/hallmark；已收录全球项目 14 个、华人项目 9 个，今日新增华人项目：Viggle AI（JST-2）。</t>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>本周 GitHub 累计星增第一是 pbakaus/impeccable；已收录全球项目 14 个、华人项目 11 个，今日新增华人项目：Teable Mobile、SpeakON Agent。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="62" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>标「✨ 今日新增」的为今天首次上榜；灰色为前 3 周周报已出现过的项目，排在最后。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="64" t="inlineStr">
+      <c r="B9" s="67" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="65" t="inlineStr">
+      <c r="B10" s="68" t="inlineStr">
         <is>
           <t>黄底：日榜第 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="66" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>橙色：🚀 单日星增速明显放大（华人项目为 ≥ 前一天 1.5 倍）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="67" t="inlineStr">
+      <c r="B12" s="70" t="inlineStr">
         <is>
           <t>灰色斜体：未查到</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="68" t="inlineStr">
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>网页版：https://psylch.github.io/rising-projects/2026-11-01/</t>
         </is>
@@ -3118,7 +3382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3190,7 +3454,7 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>https://bingxi.life/</t>
         </is>
@@ -3217,7 +3481,7 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E5" s="38" t="inlineStr">
+      <c r="E5" s="40" t="inlineStr">
         <is>
           <t>https://github.com/pancacake</t>
         </is>
@@ -3244,7 +3508,7 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2604.26962</t>
         </is>
@@ -3271,7 +3535,7 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E7" s="38" t="inlineStr">
+      <c r="E7" s="40" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/chaoh</t>
         </is>
@@ -3298,7 +3562,7 @@
           <t>GitHub 组织</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>https://github.com/HKUDS</t>
         </is>
@@ -3325,7 +3589,7 @@
           <t>来源1</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>https://datascience.hku.hk/people/chao-huang/</t>
         </is>
@@ -3352,7 +3616,7 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2604.26962</t>
         </is>
@@ -3379,7 +3643,7 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E11" s="38" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>https://github.com/Yijia-Xiao</t>
         </is>
@@ -3406,7 +3670,7 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="42" t="inlineStr">
         <is>
           <t>https://yijia-xiao.com/</t>
         </is>
@@ -3433,7 +3697,7 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E13" s="38" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>https://github.com/TauricResearch/TradingAgents</t>
         </is>
@@ -3460,7 +3724,7 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="E14" s="42" t="inlineStr">
         <is>
           <t>https://tauric.ai/contact/</t>
         </is>
@@ -3487,7 +3751,7 @@
           <t>来源4</t>
         </is>
       </c>
-      <c r="E15" s="38" t="inlineStr">
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>https://tauric.ai/research/tradingagents</t>
         </is>
@@ -3514,7 +3778,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E16" s="42" t="inlineStr">
         <is>
           <t>https://x.com/AlchainHust</t>
         </is>
@@ -3541,7 +3805,7 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E17" s="38" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/</t>
         </is>
@@ -3568,7 +3832,7 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
+      <c r="E18" s="42" t="inlineStr">
         <is>
           <t>https://github.com/alchaincyf</t>
         </is>
@@ -3595,7 +3859,7 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E19" s="38" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/insights/wechat-2247485096-1/</t>
         </is>
@@ -3622,7 +3886,7 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="42" t="inlineStr">
         <is>
           <t>https://www.huasheng.ai/consulting/</t>
         </is>
@@ -3649,7 +3913,7 @@
           <t>来源5</t>
         </is>
       </c>
-      <c r="E21" s="38" t="inlineStr">
+      <c r="E21" s="40" t="inlineStr">
         <is>
           <t>https://github.com/alchaincyf/huashu-design</t>
         </is>
@@ -3676,7 +3940,7 @@
           <t>来源6</t>
         </is>
       </c>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>https://m.okjike.com/users/27BF807A-FA4D-4B01-AAFD-05FAAA674335</t>
         </is>
@@ -3703,7 +3967,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="E23" s="38" t="inlineStr">
+      <c r="E23" s="40" t="inlineStr">
         <is>
           <t>https://x.com/xiaolai</t>
         </is>
@@ -3730,7 +3994,7 @@
           <t>个人站</t>
         </is>
       </c>
-      <c r="E24" s="35" t="inlineStr">
+      <c r="E24" s="42" t="inlineStr">
         <is>
           <t>http://lixiaolai.com</t>
         </is>
@@ -3757,7 +4021,7 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E25" s="38" t="inlineStr">
+      <c r="E25" s="40" t="inlineStr">
         <is>
           <t>https://github.com/xiaolai</t>
         </is>
@@ -3784,21 +4048,21 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E26" s="35" t="inlineStr">
+      <c r="E26" s="42" t="inlineStr">
         <is>
           <t>https://zh.wikipedia.org/wiki/%E6%9D%8E%E7%AC%91%E6%9D%A5</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+          <t>SpeakON Agent</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>樊俊超</t>
+          <t>张岩（Ryan Zhang）</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
@@ -3811,21 +4075,21 @@
           <t>来源1</t>
         </is>
       </c>
-      <c r="E27" s="38" t="inlineStr">
-        <is>
-          <t>https://wenjiai.cn/products/lanyue-ai</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+      <c r="E27" s="40" t="inlineStr">
+        <is>
+          <t>https://cn.nikkei.com/columnviewpoint/column/51907-2023-04-26-05-00-00.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+          <t>SpeakON Agent</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>樊俊超</t>
+          <t>张岩（Ryan Zhang）</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -3838,21 +4102,21 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E28" s="35" t="inlineStr">
-        <is>
-          <t>https://vc.pedaily.cn/company/865282.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+      <c r="E28" s="42" t="inlineStr">
+        <is>
+          <t>https://elsewhere.news/zh/linearcapital/boltnottaai-saas</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+          <t>SpeakON Agent</t>
         </is>
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>樊俊超</t>
+          <t>张岩（Ryan Zhang）</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
@@ -3865,21 +4129,21 @@
           <t>来源3</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/about</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+      <c r="E29" s="40" t="inlineStr">
+        <is>
+          <t>https://news.qq.com/rain/a/20260430A03LM000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+          <t>SpeakON Agent</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>樊俊超</t>
+          <t>张岩（Ryan Zhang）</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3892,264 +4156,264 @@
           <t>来源4</t>
         </is>
       </c>
-      <c r="E30" s="35" t="inlineStr">
-        <is>
-          <t>https://browser.lexmount.cn/privacy</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
+      <c r="E30" s="42" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/speakon-launches-the-first-magsafe-ai-button-built-to-replace-phone-typing-302748830.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+          <t>Teable Mobile</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>樊俊超</t>
+          <t>陈加贝（Jiabei Chen）</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/bieber-chen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Teable Mobile</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>陈加贝（Jiabei Chen）</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E32" s="42" t="inlineStr">
+        <is>
+          <t>https://x.com/thebieberchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>Teable Mobile</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>陈加贝（Jiabei Chen）</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/tea-artist</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Teable Mobile</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>陈加贝（Jiabei Chen）</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>来源5</t>
-        </is>
-      </c>
-      <c r="E31" s="38" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E32" s="35" t="inlineStr">
-        <is>
-          <t>https://github.com/ldm0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="30" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>v2ex</t>
-        </is>
-      </c>
-      <c r="E33" s="38" t="inlineStr">
-        <is>
-          <t>https://www.v2ex.com/t/1236833</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="inlineStr">
+        <is>
+          <t>https://www.teable.work/expert</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>Teable Mobile</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>陈加贝（Jiabei Chen）</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E34" s="35" t="inlineStr">
-        <is>
-          <t>https://github.com/lexmount/moli</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="inlineStr">
-        <is>
-          <t>Donough Liu（GitHub ldm0）</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>https://m.aitntnews.com/newDetail.html?newId=18503</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Teable Mobile</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>陈加贝（Jiabei Chen）</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E35" s="38" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Nico Hu</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E36" s="35" t="inlineStr">
-        <is>
-          <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E36" s="42" t="inlineStr">
+        <is>
+          <t>https://teable.ai/about</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="30" t="inlineStr">
         <is>
-          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+          <t>Teable Mobile</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>Nico Hu</t>
+          <t>Gary Guangyu Li</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E37" s="38" t="inlineStr">
-        <is>
-          <t>https://www.producthunt.com/products/lexmount-browser</t>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E37" s="40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/teable</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Viggle AI（JST-2）</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Hang Chu（中文名未查到）</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="E38" s="35" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/hang-chu</t>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E38" s="42" t="inlineStr">
+        <is>
+          <t>https://wenjiai.cn/products/lanyue-ai</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="30" t="inlineStr">
         <is>
-          <t>Viggle AI（JST-2）</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>Hang Chu（中文名未查到）</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
-          <t>个人站</t>
-        </is>
-      </c>
-      <c r="E39" s="38" t="inlineStr">
-        <is>
-          <t>http://chuhang.github.io</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E39" s="40" t="inlineStr">
+        <is>
+          <t>https://vc.pedaily.cn/company/865282.html</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Viggle AI（JST-2）</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Hang Chu（中文名未查到）</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -4159,24 +4423,24 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>来源1</t>
-        </is>
-      </c>
-      <c r="E40" s="35" t="inlineStr">
-        <is>
-          <t>http://chuhang.github.io/files/resume.pdf</t>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E40" s="42" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/about</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="30" t="inlineStr">
         <is>
-          <t>Viggle AI（JST-2）</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>Hang Chu（中文名未查到）</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
@@ -4186,24 +4450,24 @@
       </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E41" s="38" t="inlineStr">
-        <is>
-          <t>https://thelogic.co/briefing/torontos-viggle-ai-raises-us19m-series-a-led-by-a16z-for-generative-animation-tools/</t>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E41" s="40" t="inlineStr">
+        <is>
+          <t>https://browser.lexmount.cn/privacy</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>Viggle AI（JST-2）</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Hang Chu（中文名未查到）</t>
+          <t>樊俊超</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -4213,24 +4477,24 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E42" s="35" t="inlineStr">
-        <is>
-          <t>https://theorg.com/org/viggle/org-chart/hang-chu</t>
+          <t>来源5</t>
+        </is>
+      </c>
+      <c r="E42" s="42" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/chanjing/gsnews/2021-02-11/doc-ikftssap5380172.shtml</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="30" t="inlineStr">
         <is>
-          <t>hmjz100/LinkSwift</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>Hmjz100（真实姓名未查到）</t>
+          <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
@@ -4243,21 +4507,21 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="E43" s="38" t="inlineStr">
-        <is>
-          <t>https://github.com/hmjz100</t>
+      <c r="E43" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/ldm0</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>hmjz100/LinkSwift</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Hmjz100（真实姓名未查到）</t>
+          <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -4267,24 +4531,24 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>博客</t>
-        </is>
-      </c>
-      <c r="E44" s="35" t="inlineStr">
-        <is>
-          <t>https://hmjz100blog.rf.gd</t>
+          <t>v2ex</t>
+        </is>
+      </c>
+      <c r="E44" s="42" t="inlineStr">
+        <is>
+          <t>https://www.v2ex.com/t/1236833</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="30" t="inlineStr">
         <is>
-          <t>hmjz100/LinkSwift</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>Hmjz100（真实姓名未查到）</t>
+          <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
       <c r="C45" s="25" t="inlineStr">
@@ -4297,311 +4561,608 @@
           <t>来源2</t>
         </is>
       </c>
-      <c r="E45" s="38" t="inlineStr">
-        <is>
-          <t>https://github.com/hmjz100/LinkSwift</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="64" customHeight="1">
+      <c r="E45" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/lexmount/moli</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>Panniantong/Agent-Reach</t>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+          <t>Donough Liu（GitHub ldm0）</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E46" s="42" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>Nico Hu</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E46" s="35" t="inlineStr">
-        <is>
-          <t>https://x.com/Neo_Reidlab</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="64" customHeight="1">
-      <c r="A47" s="30" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B47" s="26" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C47" s="25" t="inlineStr">
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/NicoHu0701（无公开仓库，未核实）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Moli by Lexmount（揽岳智能 / 逐岳科技）</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Nico Hu</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E48" s="42" t="inlineStr">
+        <is>
+          <t>https://www.producthunt.com/products/lexmount-browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E49" s="40" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hang-chu</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>其他联系</t>
         </is>
       </c>
-      <c r="D47" s="26" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E47" s="38" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="64" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>其他联系</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>discord</t>
-        </is>
-      </c>
-      <c r="E48" s="35" t="inlineStr">
-        <is>
-          <t>https://discord.gg/NSZz22R39</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="64" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C49" s="25" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>个人站</t>
+        </is>
+      </c>
+      <c r="E50" s="42" t="inlineStr">
+        <is>
+          <t>http://chuhang.github.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>Viggle AI（JST-2）</t>
+        </is>
+      </c>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>Hang Chu（中文名未查到）</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>来源1</t>
         </is>
       </c>
-      <c r="E49" s="38" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E50" s="35" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="64" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>Panniantong/Agent-Reach</t>
-        </is>
-      </c>
-      <c r="B51" s="26" t="inlineStr">
-        <is>
-          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
-        </is>
-      </c>
-      <c r="C51" s="25" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="inlineStr">
-        <is>
-          <t>来源4</t>
-        </is>
-      </c>
-      <c r="E51" s="38" t="inlineStr">
-        <is>
-          <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
+      <c r="E51" s="40" t="inlineStr">
+        <is>
+          <t>http://chuhang.github.io/files/resume.pdf</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>Renhuai123/ziwei-doushu</t>
+          <t>Viggle AI（JST-2）</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
+          <t>Hang Chu（中文名未查到）</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E52" s="35" t="inlineStr">
-        <is>
-          <t>https://x.com/wdy188</t>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E52" s="42" t="inlineStr">
+        <is>
+          <t>https://thelogic.co/briefing/torontos-viggle-ai-raises-us19m-series-a-led-by-a16z-for-generative-animation-tools/</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="30" t="inlineStr">
         <is>
-          <t>Renhuai123/ziwei-doushu</t>
+          <t>Viggle AI（JST-2）</t>
         </is>
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
+          <t>Hang Chu（中文名未查到）</t>
         </is>
       </c>
       <c r="C53" s="25" t="inlineStr">
         <is>
-          <t>其他联系</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="D53" s="26" t="inlineStr">
         <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="E53" s="38" t="inlineStr">
-        <is>
-          <t>https://github.com/Renhuai123</t>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E53" s="40" t="inlineStr">
+        <is>
+          <t>https://theorg.com/org/viggle/org-chart/hang-chu</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>Renhuai123/ziwei-doushu</t>
+          <t>hmjz100/LinkSwift</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
+          <t>Hmjz100（真实姓名未查到）</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>来源2</t>
-        </is>
-      </c>
-      <c r="E54" s="35" t="inlineStr">
-        <is>
-          <t>https://github.com/Renhuai123/ziwei-doushu</t>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E54" s="42" t="inlineStr">
+        <is>
+          <t>https://github.com/hmjz100</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="30" t="inlineStr">
         <is>
-          <t>Renhuai123/ziwei-doushu</t>
+          <t>hmjz100/LinkSwift</t>
         </is>
       </c>
       <c r="B55" s="26" t="inlineStr">
         <is>
-          <t>王多鱼AI（网名，真实姓名未查到）</t>
+          <t>Hmjz100（真实姓名未查到）</t>
         </is>
       </c>
       <c r="C55" s="25" t="inlineStr">
         <is>
-          <t>来源</t>
+          <t>其他联系</t>
         </is>
       </c>
       <c r="D55" s="26" t="inlineStr">
         <is>
-          <t>来源3</t>
-        </is>
-      </c>
-      <c r="E55" s="38" t="inlineStr">
-        <is>
-          <t>https://metisziwei.com/privacy</t>
+          <t>博客</t>
+        </is>
+      </c>
+      <c r="E55" s="40" t="inlineStr">
+        <is>
+          <t>https://hmjz100blog.rf.gd</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
+          <t>hmjz100/LinkSwift</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Hmjz100（真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E56" s="42" t="inlineStr">
+        <is>
+          <t>https://github.com/hmjz100/LinkSwift</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="30" t="inlineStr">
+        <is>
           <t>Renhuai123/ziwei-doushu</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>王多鱼AI（网名，真实姓名未查到）</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E57" s="40" t="inlineStr">
+        <is>
+          <t>https://x.com/wdy188</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E58" s="42" t="inlineStr">
+        <is>
+          <t>https://github.com/Renhuai123</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>来源2</t>
+        </is>
+      </c>
+      <c r="E59" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E60" s="42" t="inlineStr">
+        <is>
+          <t>https://metisziwei.com/privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Renhuai123/ziwei-doushu</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>王多鱼AI（网名，真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
         <is>
           <t>来源4</t>
         </is>
       </c>
-      <c r="E56" s="35" t="inlineStr">
+      <c r="E61" s="40" t="inlineStr">
         <is>
           <t>https://zamantika.com/profile/wdy188</t>
         </is>
       </c>
     </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E62" s="42" t="inlineStr">
+        <is>
+          <t>https://x.com/Neo_Reidlab</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="E63" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="64" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>其他联系</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>discord</t>
+        </is>
+      </c>
+      <c r="E64" s="42" t="inlineStr">
+        <is>
+          <t>https://discord.gg/NSZz22R39</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="64" customHeight="1">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B65" s="26" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>来源1</t>
+        </is>
+      </c>
+      <c r="E65" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>来源3</t>
+        </is>
+      </c>
+      <c r="E66" s="42" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Panniantong/Panniantong/main/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="64" customHeight="1">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Panniantong/Agent-Reach</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="inlineStr">
+        <is>
+          <t>Neo Reid（英文名/网名；GitHub 显示名 Pnant / login Panniantong；中文真实姓名未查到）</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>来源4</t>
+        </is>
+      </c>
+      <c r="E67" s="40" t="inlineStr">
+        <is>
+          <t>https://github.com/Panniantong/Agent-Reach/blob/main/pyproject.toml</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:E56"/>
+  <autoFilter ref="A3:E67"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -4660,6 +5221,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId64"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
